--- a/research/traditional_assets/database/data/brazil/brazil_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_chemical_basic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1152685924699146</v>
+        <v>0.1149063792555169</v>
       </c>
       <c r="C2">
-        <v>191.5849323913017</v>
+        <v>190.0476207599566</v>
       </c>
       <c r="D2">
-        <v>119.5849323913016</v>
+        <v>120.0146207599566</v>
       </c>
       <c r="E2">
-        <v>-49.3</v>
+        <v>-47.333</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.967</v>
       </c>
       <c r="G2">
         <v>72</v>
@@ -1451,28 +1451,28 @@
         <v>40.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.09894009999999999</v>
       </c>
       <c r="N2">
-        <v>40.5</v>
+        <v>40.4010599</v>
       </c>
       <c r="O2">
-        <v>13.77</v>
+        <v>13.736360366</v>
       </c>
       <c r="P2">
-        <v>26.73</v>
+        <v>26.664699534</v>
       </c>
       <c r="Q2">
-        <v>32.02999999999999</v>
+        <v>31.964699534</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1152685924699146</v>
+        <v>0.115731716419714</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470865</v>
+        <v>0.9114446971440671</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>409.338579605236</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1149063792555169</v>
+        <v>0.1145441660411192</v>
       </c>
       <c r="C3">
-        <v>190.0476207599566</v>
+        <v>188.5134081461273</v>
       </c>
       <c r="D3">
-        <v>120.0146207599566</v>
+        <v>120.4474081461272</v>
       </c>
       <c r="E3">
-        <v>-47.333</v>
+        <v>-45.366</v>
       </c>
       <c r="F3">
-        <v>1.967</v>
+        <v>3.934</v>
       </c>
       <c r="G3">
         <v>72</v>
@@ -1533,28 +1533,28 @@
         <v>40.5</v>
       </c>
       <c r="M3">
-        <v>0.09894009999999999</v>
+        <v>0.1978802</v>
       </c>
       <c r="N3">
-        <v>40.4010599</v>
+        <v>40.3021198</v>
       </c>
       <c r="O3">
-        <v>13.736360366</v>
+        <v>13.702720732</v>
       </c>
       <c r="P3">
-        <v>26.664699534</v>
+        <v>26.599399068</v>
       </c>
       <c r="Q3">
-        <v>31.964699534</v>
+        <v>31.89939906799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.115731716419714</v>
+        <v>0.116204291878693</v>
       </c>
       <c r="T3">
-        <v>0.9114446971440671</v>
+        <v>0.9176039395899656</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>409.338579605236</v>
+        <v>204.669289802618</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1145441660411192</v>
+        <v>0.1141819528267215</v>
       </c>
       <c r="C4">
-        <v>188.5134081461273</v>
+        <v>186.9823281974585</v>
       </c>
       <c r="D4">
-        <v>120.4474081461272</v>
+        <v>120.8833281974585</v>
       </c>
       <c r="E4">
-        <v>-45.366</v>
+        <v>-43.399</v>
       </c>
       <c r="F4">
-        <v>3.934</v>
+        <v>5.901</v>
       </c>
       <c r="G4">
         <v>72</v>
@@ -1615,28 +1615,28 @@
         <v>40.5</v>
       </c>
       <c r="M4">
-        <v>0.1978802</v>
+        <v>0.2968203</v>
       </c>
       <c r="N4">
-        <v>40.3021198</v>
+        <v>40.2031797</v>
       </c>
       <c r="O4">
-        <v>13.702720732</v>
+        <v>13.669081098</v>
       </c>
       <c r="P4">
-        <v>26.599399068</v>
+        <v>26.534098602</v>
       </c>
       <c r="Q4">
-        <v>31.89939906799999</v>
+        <v>31.834098602</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.116204291878693</v>
+        <v>0.1166866111615685</v>
       </c>
       <c r="T4">
-        <v>0.9176039395899656</v>
+        <v>0.9238901767254705</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>204.669289802618</v>
+        <v>136.4461932017453</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1141819528267215</v>
+        <v>0.1138197396123238</v>
       </c>
       <c r="C5">
-        <v>186.9823281974585</v>
+        <v>185.4544150504714</v>
       </c>
       <c r="D5">
-        <v>120.8833281974585</v>
+        <v>121.3224150504714</v>
       </c>
       <c r="E5">
-        <v>-43.399</v>
+        <v>-41.432</v>
       </c>
       <c r="F5">
-        <v>5.901</v>
+        <v>7.867999999999999</v>
       </c>
       <c r="G5">
         <v>72</v>
@@ -1697,28 +1697,28 @@
         <v>40.5</v>
       </c>
       <c r="M5">
-        <v>0.2968203</v>
+        <v>0.3957604</v>
       </c>
       <c r="N5">
-        <v>40.2031797</v>
+        <v>40.1042396</v>
       </c>
       <c r="O5">
-        <v>13.669081098</v>
+        <v>13.635441464</v>
       </c>
       <c r="P5">
-        <v>26.534098602</v>
+        <v>26.468798136</v>
       </c>
       <c r="Q5">
-        <v>31.834098602</v>
+        <v>31.76879813599999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1166866111615685</v>
+        <v>0.1171789787628373</v>
       </c>
       <c r="T5">
-        <v>0.9238901767254705</v>
+        <v>0.9303073771346314</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>136.4461932017453</v>
+        <v>102.334644901309</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1138197396123238</v>
+        <v>0.113457526397926</v>
       </c>
       <c r="C6">
-        <v>185.4544150504714</v>
+        <v>183.9297033394738</v>
       </c>
       <c r="D6">
-        <v>121.3224150504714</v>
+        <v>121.7647033394738</v>
       </c>
       <c r="E6">
-        <v>-41.432</v>
+        <v>-39.465</v>
       </c>
       <c r="F6">
-        <v>7.867999999999999</v>
+        <v>9.835000000000001</v>
       </c>
       <c r="G6">
         <v>72</v>
@@ -1779,28 +1779,28 @@
         <v>40.5</v>
       </c>
       <c r="M6">
-        <v>0.3957604</v>
+        <v>0.4947005</v>
       </c>
       <c r="N6">
-        <v>40.1042396</v>
+        <v>40.0052995</v>
       </c>
       <c r="O6">
-        <v>13.635441464</v>
+        <v>13.60180183</v>
       </c>
       <c r="P6">
-        <v>26.468798136</v>
+        <v>26.40349767</v>
       </c>
       <c r="Q6">
-        <v>31.76879813599999</v>
+        <v>31.70349767</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1171789787628373</v>
+        <v>0.1176817119978169</v>
       </c>
       <c r="T6">
-        <v>0.9303073771346314</v>
+        <v>0.9368596764997748</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>102.334644901309</v>
+        <v>81.86771592104716</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.113457526397926</v>
+        <v>0.1130953131835283</v>
       </c>
       <c r="C7">
-        <v>183.9297033394738</v>
+        <v>182.4082282056677</v>
       </c>
       <c r="D7">
-        <v>121.7647033394738</v>
+        <v>122.2102282056677</v>
       </c>
       <c r="E7">
-        <v>-39.465</v>
+        <v>-37.498</v>
       </c>
       <c r="F7">
-        <v>9.835000000000001</v>
+        <v>11.802</v>
       </c>
       <c r="G7">
         <v>72</v>
@@ -1861,28 +1861,28 @@
         <v>40.5</v>
       </c>
       <c r="M7">
-        <v>0.4947005</v>
+        <v>0.5936406</v>
       </c>
       <c r="N7">
-        <v>40.0052995</v>
+        <v>39.9063594</v>
       </c>
       <c r="O7">
-        <v>13.60180183</v>
+        <v>13.568162196</v>
       </c>
       <c r="P7">
-        <v>26.40349767</v>
+        <v>26.338197204</v>
       </c>
       <c r="Q7">
-        <v>31.70349767</v>
+        <v>31.63819720399999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1176817119978169</v>
+        <v>0.1181951416846046</v>
       </c>
       <c r="T7">
-        <v>0.9368596764997748</v>
+        <v>0.9435513864897085</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>81.86771592104716</v>
+        <v>68.22309660087265</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1130953131835283</v>
+        <v>0.1127330999691306</v>
       </c>
       <c r="C8">
-        <v>182.4082282056677</v>
+        <v>180.8900253064563</v>
       </c>
       <c r="D8">
-        <v>122.2102282056677</v>
+        <v>122.6590253064563</v>
       </c>
       <c r="E8">
-        <v>-37.498</v>
+        <v>-35.531</v>
       </c>
       <c r="F8">
-        <v>11.802</v>
+        <v>13.769</v>
       </c>
       <c r="G8">
         <v>72</v>
@@ -1943,28 +1943,28 @@
         <v>40.5</v>
       </c>
       <c r="M8">
-        <v>0.5936406</v>
+        <v>0.6925806999999999</v>
       </c>
       <c r="N8">
-        <v>39.9063594</v>
+        <v>39.8074193</v>
       </c>
       <c r="O8">
-        <v>13.568162196</v>
+        <v>13.534522562</v>
       </c>
       <c r="P8">
-        <v>26.338197204</v>
+        <v>26.272896738</v>
       </c>
       <c r="Q8">
-        <v>31.63819720399999</v>
+        <v>31.572896738</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1181951416846046</v>
+        <v>0.1187196128700329</v>
       </c>
       <c r="T8">
-        <v>0.9435513864897085</v>
+        <v>0.950387004221361</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>68.22309660087265</v>
+        <v>58.47693994360513</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1127330999691306</v>
+        <v>0.1123708867547329</v>
       </c>
       <c r="C9">
-        <v>180.8900253064563</v>
+        <v>179.3751308249572</v>
       </c>
       <c r="D9">
-        <v>122.6590253064563</v>
+        <v>123.1111308249572</v>
       </c>
       <c r="E9">
-        <v>-35.531</v>
+        <v>-33.564</v>
       </c>
       <c r="F9">
-        <v>13.769</v>
+        <v>15.736</v>
       </c>
       <c r="G9">
         <v>72</v>
@@ -2025,28 +2025,28 @@
         <v>40.5</v>
       </c>
       <c r="M9">
-        <v>0.6925806999999999</v>
+        <v>0.7915207999999999</v>
       </c>
       <c r="N9">
-        <v>39.8074193</v>
+        <v>39.7084792</v>
       </c>
       <c r="O9">
-        <v>13.534522562</v>
+        <v>13.500882928</v>
       </c>
       <c r="P9">
-        <v>26.272896738</v>
+        <v>26.207596272</v>
       </c>
       <c r="Q9">
-        <v>31.572896738</v>
+        <v>31.50759627199999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1187196128700329</v>
+        <v>0.1192554856029706</v>
       </c>
       <c r="T9">
-        <v>0.9503870042213612</v>
+        <v>0.9573712223384845</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>58.47693994360513</v>
+        <v>51.16732245065449</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1123708867547329</v>
+        <v>0.1120086735403352</v>
       </c>
       <c r="C10">
-        <v>179.3751308249572</v>
+        <v>177.8635814797272</v>
       </c>
       <c r="D10">
-        <v>123.1111308249572</v>
+        <v>123.5665814797272</v>
       </c>
       <c r="E10">
-        <v>-33.564</v>
+        <v>-31.597</v>
       </c>
       <c r="F10">
-        <v>15.736</v>
+        <v>17.703</v>
       </c>
       <c r="G10">
         <v>72</v>
@@ -2107,28 +2107,28 @@
         <v>40.5</v>
       </c>
       <c r="M10">
-        <v>0.7915207999999999</v>
+        <v>0.8904608999999999</v>
       </c>
       <c r="N10">
-        <v>39.7084792</v>
+        <v>39.6095391</v>
       </c>
       <c r="O10">
-        <v>13.500882928</v>
+        <v>13.467243294</v>
       </c>
       <c r="P10">
-        <v>26.207596272</v>
+        <v>26.142295806</v>
       </c>
       <c r="Q10">
-        <v>31.50759627199999</v>
+        <v>31.442295806</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1192554856029706</v>
+        <v>0.1198031357586101</v>
       </c>
       <c r="T10">
-        <v>0.9573712223384845</v>
+        <v>0.9645089397548853</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>51.16732245065449</v>
+        <v>45.48206440058177</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1120086735403352</v>
+        <v>0.1116464603259375</v>
       </c>
       <c r="C11">
-        <v>177.8635814797272</v>
+        <v>176.3554145347032</v>
       </c>
       <c r="D11">
-        <v>123.5665814797272</v>
+        <v>124.0254145347032</v>
       </c>
       <c r="E11">
-        <v>-31.597</v>
+        <v>-29.63</v>
       </c>
       <c r="F11">
-        <v>17.703</v>
+        <v>19.67</v>
       </c>
       <c r="G11">
         <v>72</v>
@@ -2189,28 +2189,28 @@
         <v>40.5</v>
       </c>
       <c r="M11">
-        <v>0.8904608999999999</v>
+        <v>0.9894009999999999</v>
       </c>
       <c r="N11">
-        <v>39.6095391</v>
+        <v>39.510599</v>
       </c>
       <c r="O11">
-        <v>13.467243294</v>
+        <v>13.43360366</v>
       </c>
       <c r="P11">
-        <v>26.142295806</v>
+        <v>26.07699534</v>
       </c>
       <c r="Q11">
-        <v>31.442295806</v>
+        <v>31.37699533999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1198031357586101</v>
+        <v>0.1203629559177083</v>
       </c>
       <c r="T11">
-        <v>0.9645089397548853</v>
+        <v>0.9718052731138728</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>45.48206440058177</v>
+        <v>40.9338579605236</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1116464603259375</v>
+        <v>0.1112842471115398</v>
       </c>
       <c r="C12">
-        <v>176.3554145347032</v>
+        <v>174.8506678093652</v>
       </c>
       <c r="D12">
-        <v>124.0254145347032</v>
+        <v>124.4876678093652</v>
       </c>
       <c r="E12">
-        <v>-29.63</v>
+        <v>-27.663</v>
       </c>
       <c r="F12">
-        <v>19.67</v>
+        <v>21.637</v>
       </c>
       <c r="G12">
         <v>72</v>
@@ -2271,28 +2271,28 @@
         <v>40.5</v>
       </c>
       <c r="M12">
-        <v>0.9894010000000001</v>
+        <v>1.0883411</v>
       </c>
       <c r="N12">
-        <v>39.510599</v>
+        <v>39.4116589</v>
       </c>
       <c r="O12">
-        <v>13.43360366</v>
+        <v>13.399964026</v>
       </c>
       <c r="P12">
-        <v>26.07699534</v>
+        <v>26.011694874</v>
       </c>
       <c r="Q12">
-        <v>31.37699533999999</v>
+        <v>31.311694874</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1203629559177083</v>
+        <v>0.1209353563051009</v>
       </c>
       <c r="T12">
-        <v>0.9718052731138728</v>
+        <v>0.9792655690202532</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>40.93385796052358</v>
+        <v>37.21259814593054</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1112842471115398</v>
+        <v>0.1109220338971421</v>
       </c>
       <c r="C13">
-        <v>174.8506678093652</v>
+        <v>173.3493796891286</v>
       </c>
       <c r="D13">
-        <v>124.4876678093652</v>
+        <v>124.9533796891286</v>
       </c>
       <c r="E13">
-        <v>-27.663</v>
+        <v>-25.696</v>
       </c>
       <c r="F13">
-        <v>21.637</v>
+        <v>23.604</v>
       </c>
       <c r="G13">
         <v>72</v>
@@ -2353,28 +2353,28 @@
         <v>40.5</v>
       </c>
       <c r="M13">
-        <v>1.0883411</v>
+        <v>1.1872812</v>
       </c>
       <c r="N13">
-        <v>39.4116589</v>
+        <v>39.3127188</v>
       </c>
       <c r="O13">
-        <v>13.399964026</v>
+        <v>13.366324392</v>
       </c>
       <c r="P13">
-        <v>26.011694874</v>
+        <v>25.946394408</v>
       </c>
       <c r="Q13">
-        <v>31.311694874</v>
+        <v>31.24639440799999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1209353563051009</v>
+        <v>0.1215207657922069</v>
       </c>
       <c r="T13">
-        <v>0.9792655690202532</v>
+        <v>0.9868954171063243</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>37.21259814593054</v>
+        <v>34.11154830043633</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1109220338971421</v>
+        <v>0.1105598206827444</v>
       </c>
       <c r="C14">
-        <v>173.3493796891286</v>
+        <v>171.8515891359691</v>
       </c>
       <c r="D14">
-        <v>124.9533796891286</v>
+        <v>125.4225891359691</v>
       </c>
       <c r="E14">
-        <v>-25.696</v>
+        <v>-23.729</v>
       </c>
       <c r="F14">
-        <v>23.604</v>
+        <v>25.571</v>
       </c>
       <c r="G14">
         <v>72</v>
@@ -2435,28 +2435,28 @@
         <v>40.5</v>
       </c>
       <c r="M14">
-        <v>1.1872812</v>
+        <v>1.2862213</v>
       </c>
       <c r="N14">
-        <v>39.3127188</v>
+        <v>39.2137787</v>
       </c>
       <c r="O14">
-        <v>13.366324392</v>
+        <v>13.332684758</v>
       </c>
       <c r="P14">
-        <v>25.946394408</v>
+        <v>25.881093942</v>
       </c>
       <c r="Q14">
-        <v>31.24639440799999</v>
+        <v>31.181093942</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1215207657922069</v>
+        <v>0.1221196329686717</v>
       </c>
       <c r="T14">
-        <v>0.9868954171063243</v>
+        <v>0.9947006639989716</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>34.11154830043633</v>
+        <v>31.48758304655661</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1105598206827444</v>
+        <v>0.1101976074683466</v>
       </c>
       <c r="C15">
-        <v>171.8515891359691</v>
+        <v>170.3573356992893</v>
       </c>
       <c r="D15">
-        <v>125.4225891359691</v>
+        <v>125.8953356992893</v>
       </c>
       <c r="E15">
-        <v>-23.729</v>
+        <v>-21.762</v>
       </c>
       <c r="F15">
-        <v>25.571</v>
+        <v>27.538</v>
       </c>
       <c r="G15">
         <v>72</v>
@@ -2517,28 +2517,28 @@
         <v>40.5</v>
       </c>
       <c r="M15">
-        <v>1.2862213</v>
+        <v>1.3851614</v>
       </c>
       <c r="N15">
-        <v>39.2137787</v>
+        <v>39.1148386</v>
       </c>
       <c r="O15">
-        <v>13.332684758</v>
+        <v>13.299045124</v>
       </c>
       <c r="P15">
-        <v>25.881093942</v>
+        <v>25.815793476</v>
       </c>
       <c r="Q15">
-        <v>31.181093942</v>
+        <v>31.11579347599999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1221196329686717</v>
+        <v>0.1227324272887752</v>
       </c>
       <c r="T15">
-        <v>0.9947006639989716</v>
+        <v>1.002687428261215</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>31.48758304655661</v>
+        <v>29.23846997180257</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1101976074683466</v>
+        <v>0.109835394253949</v>
       </c>
       <c r="C16">
-        <v>170.3573356992893</v>
+        <v>168.8666595270305</v>
       </c>
       <c r="D16">
-        <v>125.8953356992893</v>
+        <v>126.3716595270305</v>
       </c>
       <c r="E16">
-        <v>-21.762</v>
+        <v>-19.79499999999999</v>
       </c>
       <c r="F16">
-        <v>27.538</v>
+        <v>29.505</v>
       </c>
       <c r="G16">
         <v>72</v>
@@ -2599,28 +2599,28 @@
         <v>40.5</v>
       </c>
       <c r="M16">
-        <v>1.3851614</v>
+        <v>1.4841015</v>
       </c>
       <c r="N16">
-        <v>39.1148386</v>
+        <v>39.0158985</v>
       </c>
       <c r="O16">
-        <v>13.299045124</v>
+        <v>13.26540549</v>
       </c>
       <c r="P16">
-        <v>25.815793476</v>
+        <v>25.75049301</v>
       </c>
       <c r="Q16">
-        <v>31.11579347599999</v>
+        <v>31.05049301</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1227324272887752</v>
+        <v>0.1233596402987635</v>
       </c>
       <c r="T16">
-        <v>1.002687428261215</v>
+        <v>1.010862116388453</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>29.23846997180257</v>
+        <v>27.28923864034906</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.109835394253949</v>
+        <v>0.1094731810395512</v>
       </c>
       <c r="C17">
-        <v>168.8666595270305</v>
+        <v>167.3796013770395</v>
       </c>
       <c r="D17">
-        <v>126.3716595270305</v>
+        <v>126.8516013770395</v>
       </c>
       <c r="E17">
-        <v>-19.795</v>
+        <v>-17.828</v>
       </c>
       <c r="F17">
-        <v>29.505</v>
+        <v>31.472</v>
       </c>
       <c r="G17">
         <v>72</v>
@@ -2681,28 +2681,28 @@
         <v>40.5</v>
       </c>
       <c r="M17">
-        <v>1.4841015</v>
+        <v>1.5830416</v>
       </c>
       <c r="N17">
-        <v>39.0158985</v>
+        <v>38.9169584</v>
       </c>
       <c r="O17">
-        <v>13.26540549</v>
+        <v>13.231765856</v>
       </c>
       <c r="P17">
-        <v>25.75049301</v>
+        <v>25.685192544</v>
       </c>
       <c r="Q17">
-        <v>31.05049301</v>
+        <v>30.98519254399999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1233596402987635</v>
+        <v>0.1240017869518467</v>
       </c>
       <c r="T17">
-        <v>1.010862116388453</v>
+        <v>1.019231439947292</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>27.28923864034906</v>
+        <v>25.58366122532724</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1094731810395512</v>
+        <v>0.1091109678251535</v>
       </c>
       <c r="C18">
-        <v>167.3796013770395</v>
+        <v>165.8962026286937</v>
       </c>
       <c r="D18">
-        <v>126.8516013770395</v>
+        <v>127.3352026286937</v>
       </c>
       <c r="E18">
-        <v>-17.828</v>
+        <v>-15.861</v>
       </c>
       <c r="F18">
-        <v>31.472</v>
+        <v>33.439</v>
       </c>
       <c r="G18">
         <v>72</v>
@@ -2763,28 +2763,28 @@
         <v>40.5</v>
       </c>
       <c r="M18">
-        <v>1.5830416</v>
+        <v>1.6819817</v>
       </c>
       <c r="N18">
-        <v>38.9169584</v>
+        <v>38.8180183</v>
       </c>
       <c r="O18">
-        <v>13.231765856</v>
+        <v>13.198126222</v>
       </c>
       <c r="P18">
-        <v>25.685192544</v>
+        <v>25.619892078</v>
       </c>
       <c r="Q18">
-        <v>30.98519254399999</v>
+        <v>30.919892078</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1240017869518467</v>
+        <v>0.1246594070182573</v>
       </c>
       <c r="T18">
-        <v>1.019231439947292</v>
+        <v>1.027802433953331</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>25.58366122532724</v>
+        <v>24.07873997677858</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1091109678251535</v>
+        <v>0.1087487546107558</v>
       </c>
       <c r="C19">
-        <v>165.8962026286937</v>
+        <v>164.4165052947941</v>
       </c>
       <c r="D19">
-        <v>127.3352026286937</v>
+        <v>127.8225052947941</v>
       </c>
       <c r="E19">
-        <v>-15.861</v>
+        <v>-13.894</v>
       </c>
       <c r="F19">
-        <v>33.439</v>
+        <v>35.406</v>
       </c>
       <c r="G19">
         <v>72</v>
@@ -2845,28 +2845,28 @@
         <v>40.5</v>
       </c>
       <c r="M19">
-        <v>1.6819817</v>
+        <v>1.7809218</v>
       </c>
       <c r="N19">
-        <v>38.8180183</v>
+        <v>38.7190782</v>
       </c>
       <c r="O19">
-        <v>13.198126222</v>
+        <v>13.164486588</v>
       </c>
       <c r="P19">
-        <v>25.619892078</v>
+        <v>25.554591612</v>
       </c>
       <c r="Q19">
-        <v>30.919892078</v>
+        <v>30.85459161199999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1246594070182573</v>
+        <v>0.1253330665984827</v>
       </c>
       <c r="T19">
-        <v>1.027802433953331</v>
+        <v>1.036582476593664</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>24.07873997677858</v>
+        <v>22.74103220029088</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1087487546107558</v>
+        <v>0.1083865413963581</v>
       </c>
       <c r="C20">
-        <v>164.416505294794</v>
+        <v>162.9405520337322</v>
       </c>
       <c r="D20">
-        <v>127.822505294794</v>
+        <v>128.3135520337322</v>
       </c>
       <c r="E20">
-        <v>-13.894</v>
+        <v>-11.927</v>
       </c>
       <c r="F20">
-        <v>35.406</v>
+        <v>37.373</v>
       </c>
       <c r="G20">
         <v>72</v>
@@ -2927,28 +2927,28 @@
         <v>40.5</v>
       </c>
       <c r="M20">
-        <v>1.7809218</v>
+        <v>1.8798619</v>
       </c>
       <c r="N20">
-        <v>38.7190782</v>
+        <v>38.6201381</v>
       </c>
       <c r="O20">
-        <v>13.164486588</v>
+        <v>13.130846954</v>
       </c>
       <c r="P20">
-        <v>25.554591612</v>
+        <v>25.489291146</v>
       </c>
       <c r="Q20">
-        <v>30.85459161199999</v>
+        <v>30.789291146</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1253330665984827</v>
+        <v>0.1260233597485902</v>
       </c>
       <c r="T20">
-        <v>1.036582476593664</v>
+        <v>1.045579310410302</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>22.74103220029088</v>
+        <v>21.54413576869663</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1083865413963581</v>
+        <v>0.1080243281819604</v>
       </c>
       <c r="C21">
-        <v>162.9405520337322</v>
+        <v>161.4683861619385</v>
       </c>
       <c r="D21">
-        <v>128.3135520337322</v>
+        <v>128.8083861619385</v>
       </c>
       <c r="E21">
-        <v>-11.927</v>
+        <v>-9.959999999999994</v>
       </c>
       <c r="F21">
-        <v>37.373</v>
+        <v>39.34</v>
       </c>
       <c r="G21">
         <v>72</v>
@@ -3009,28 +3009,28 @@
         <v>40.5</v>
       </c>
       <c r="M21">
-        <v>1.8798619</v>
+        <v>1.978802</v>
       </c>
       <c r="N21">
-        <v>38.6201381</v>
+        <v>38.521198</v>
       </c>
       <c r="O21">
-        <v>13.130846954</v>
+        <v>13.09720732</v>
       </c>
       <c r="P21">
-        <v>25.489291146</v>
+        <v>25.42399068</v>
       </c>
       <c r="Q21">
-        <v>30.789291146</v>
+        <v>30.72399067999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1260233597485902</v>
+        <v>0.1267309102274505</v>
       </c>
       <c r="T21">
-        <v>1.045579310410302</v>
+        <v>1.054801065072356</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>21.54413576869663</v>
+        <v>20.46692898026179</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1080243281819604</v>
+        <v>0.1076621149675627</v>
       </c>
       <c r="C22">
-        <v>161.4683861619385</v>
+        <v>160.0000516666201</v>
       </c>
       <c r="D22">
-        <v>128.8083861619385</v>
+        <v>129.3070516666201</v>
       </c>
       <c r="E22">
-        <v>-9.959999999999994</v>
+        <v>-7.992999999999995</v>
       </c>
       <c r="F22">
-        <v>39.34</v>
+        <v>41.307</v>
       </c>
       <c r="G22">
         <v>72</v>
@@ -3091,28 +3091,28 @@
         <v>40.5</v>
       </c>
       <c r="M22">
-        <v>1.978802</v>
+        <v>2.0777421</v>
       </c>
       <c r="N22">
-        <v>38.521198</v>
+        <v>38.4222579</v>
       </c>
       <c r="O22">
-        <v>13.09720732</v>
+        <v>13.063567686</v>
       </c>
       <c r="P22">
-        <v>25.42399068</v>
+        <v>25.358690214</v>
       </c>
       <c r="Q22">
-        <v>30.72399067999999</v>
+        <v>30.658690214</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1267309102274505</v>
+        <v>0.1274563733766616</v>
       </c>
       <c r="T22">
-        <v>1.054801065072356</v>
+        <v>1.064256281877753</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>20.46692898026179</v>
+        <v>19.49231331453504</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1076621149675627</v>
+        <v>0.107299901753165</v>
       </c>
       <c r="C23">
-        <v>160.0000516666201</v>
+        <v>158.535593218795</v>
       </c>
       <c r="D23">
-        <v>129.3070516666201</v>
+        <v>129.809593218795</v>
       </c>
       <c r="E23">
-        <v>-7.993000000000002</v>
+        <v>-6.025999999999996</v>
       </c>
       <c r="F23">
-        <v>41.307</v>
+        <v>43.274</v>
       </c>
       <c r="G23">
         <v>72</v>
@@ -3173,28 +3173,28 @@
         <v>40.5</v>
       </c>
       <c r="M23">
-        <v>2.0777421</v>
+        <v>2.1766822</v>
       </c>
       <c r="N23">
-        <v>38.4222579</v>
+        <v>38.3233178</v>
       </c>
       <c r="O23">
-        <v>13.063567686</v>
+        <v>13.029928052</v>
       </c>
       <c r="P23">
-        <v>25.358690214</v>
+        <v>25.293389748</v>
       </c>
       <c r="Q23">
-        <v>30.658690214</v>
+        <v>30.59338974799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1274563733766616</v>
+        <v>0.1282004381450833</v>
       </c>
       <c r="T23">
-        <v>1.064256281877752</v>
+        <v>1.073953940139698</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>19.49231331453505</v>
+        <v>18.60629907296527</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.107299901753165</v>
+        <v>0.1069376885387673</v>
       </c>
       <c r="C24">
-        <v>158.535593218795</v>
+        <v>157.0750561866321</v>
       </c>
       <c r="D24">
-        <v>129.809593218795</v>
+        <v>130.3160561866321</v>
       </c>
       <c r="E24">
-        <v>-6.025999999999996</v>
+        <v>-4.058999999999997</v>
       </c>
       <c r="F24">
-        <v>43.274</v>
+        <v>45.241</v>
       </c>
       <c r="G24">
         <v>72</v>
@@ -3255,28 +3255,28 @@
         <v>40.5</v>
       </c>
       <c r="M24">
-        <v>2.1766822</v>
+        <v>2.2756223</v>
       </c>
       <c r="N24">
-        <v>38.3233178</v>
+        <v>38.2243777</v>
       </c>
       <c r="O24">
-        <v>13.029928052</v>
+        <v>12.996288418</v>
       </c>
       <c r="P24">
-        <v>25.293389748</v>
+        <v>25.228089282</v>
       </c>
       <c r="Q24">
-        <v>30.59338974799999</v>
+        <v>30.528089282</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1282004381450833</v>
+        <v>0.1289638292711263</v>
       </c>
       <c r="T24">
-        <v>1.073953940139698</v>
+        <v>1.083903485629226</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>18.60629907296527</v>
+        <v>17.79732954805374</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1069376885387673</v>
+        <v>0.1065754753243696</v>
       </c>
       <c r="C25">
-        <v>157.0750561866321</v>
+        <v>155.6184866491043</v>
       </c>
       <c r="D25">
-        <v>130.3160561866321</v>
+        <v>130.8264866491043</v>
       </c>
       <c r="E25">
-        <v>-4.058999999999997</v>
+        <v>-2.091999999999999</v>
       </c>
       <c r="F25">
-        <v>45.241</v>
+        <v>47.208</v>
       </c>
       <c r="G25">
         <v>72</v>
@@ -3337,28 +3337,28 @@
         <v>40.5</v>
       </c>
       <c r="M25">
-        <v>2.2756223</v>
+        <v>2.3745624</v>
       </c>
       <c r="N25">
-        <v>38.2243777</v>
+        <v>38.1254376</v>
       </c>
       <c r="O25">
-        <v>12.996288418</v>
+        <v>12.962648784</v>
       </c>
       <c r="P25">
-        <v>25.228089282</v>
+        <v>25.162788816</v>
       </c>
       <c r="Q25">
-        <v>30.528089282</v>
+        <v>30.46278881599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1289638292711263</v>
+        <v>0.1297473096373284</v>
       </c>
       <c r="T25">
-        <v>1.083903485629226</v>
+        <v>1.094114861263216</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>17.79732954805374</v>
+        <v>17.05577415021816</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1065754753243695</v>
+        <v>0.1062132621099719</v>
       </c>
       <c r="C26">
-        <v>155.6184866491043</v>
+        <v>154.1659314099641</v>
       </c>
       <c r="D26">
-        <v>130.8264866491043</v>
+        <v>131.3409314099641</v>
       </c>
       <c r="E26">
-        <v>-2.091999999999999</v>
+        <v>-0.125</v>
       </c>
       <c r="F26">
-        <v>47.208</v>
+        <v>49.175</v>
       </c>
       <c r="G26">
         <v>72</v>
@@ -3419,28 +3419,28 @@
         <v>40.5</v>
       </c>
       <c r="M26">
-        <v>2.3745624</v>
+        <v>2.4735025</v>
       </c>
       <c r="N26">
-        <v>38.1254376</v>
+        <v>38.0264975</v>
       </c>
       <c r="O26">
-        <v>12.962648784</v>
+        <v>12.92900915</v>
       </c>
       <c r="P26">
-        <v>25.162788816</v>
+        <v>25.09748835</v>
       </c>
       <c r="Q26">
-        <v>30.46278881599999</v>
+        <v>30.39748835</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1297473096373284</v>
+        <v>0.1305516828132958</v>
       </c>
       <c r="T26">
-        <v>1.094114861263216</v>
+        <v>1.104598540247445</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>17.05577415021816</v>
+        <v>16.37354318420943</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1062132621099719</v>
+        <v>0.1058510488955742</v>
       </c>
       <c r="C27">
-        <v>154.1659314099641</v>
+        <v>152.7174380120496</v>
       </c>
       <c r="D27">
-        <v>131.3409314099641</v>
+        <v>131.8594380120496</v>
       </c>
       <c r="E27">
-        <v>-0.125</v>
+        <v>1.841999999999999</v>
       </c>
       <c r="F27">
-        <v>49.175</v>
+        <v>51.142</v>
       </c>
       <c r="G27">
         <v>72</v>
@@ -3501,28 +3501,28 @@
         <v>40.5</v>
       </c>
       <c r="M27">
-        <v>2.4735025</v>
+        <v>2.5724426</v>
       </c>
       <c r="N27">
-        <v>38.0264975</v>
+        <v>37.9275574</v>
       </c>
       <c r="O27">
-        <v>12.92900915</v>
+        <v>12.895369516</v>
       </c>
       <c r="P27">
-        <v>25.09748835</v>
+        <v>25.032187884</v>
       </c>
       <c r="Q27">
-        <v>30.39748835</v>
+        <v>30.33218788399999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1305516828132958</v>
+        <v>0.1313777958048299</v>
       </c>
       <c r="T27">
-        <v>1.104598540247445</v>
+        <v>1.115365561906924</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>16.37354318420943</v>
+        <v>15.74379152327831</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1058510488955742</v>
+        <v>0.1054888356811764</v>
       </c>
       <c r="C28">
-        <v>152.7174380120496</v>
+        <v>151.2730547519315</v>
       </c>
       <c r="D28">
-        <v>131.8594380120496</v>
+        <v>132.3820547519315</v>
       </c>
       <c r="E28">
-        <v>1.841999999999999</v>
+        <v>3.809000000000005</v>
       </c>
       <c r="F28">
-        <v>51.142</v>
+        <v>53.109</v>
       </c>
       <c r="G28">
         <v>72</v>
@@ -3583,28 +3583,28 @@
         <v>40.5</v>
       </c>
       <c r="M28">
-        <v>2.5724426</v>
+        <v>2.6713827</v>
       </c>
       <c r="N28">
-        <v>37.9275574</v>
+        <v>37.8286173</v>
       </c>
       <c r="O28">
-        <v>12.895369516</v>
+        <v>12.861729882</v>
       </c>
       <c r="P28">
-        <v>25.032187884</v>
+        <v>24.966887418</v>
       </c>
       <c r="Q28">
-        <v>30.33218788399999</v>
+        <v>30.266887418</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1313777958048299</v>
+        <v>0.1322265420290088</v>
       </c>
       <c r="T28">
-        <v>1.115365561906924</v>
+        <v>1.126427570461183</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>15.74379152327831</v>
+        <v>15.16068813352725</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1054888356811764</v>
+        <v>0.1051266224667787</v>
       </c>
       <c r="C29">
-        <v>151.2730547519315</v>
+        <v>149.8328306949091</v>
       </c>
       <c r="D29">
-        <v>132.3820547519315</v>
+        <v>132.9088306949091</v>
       </c>
       <c r="E29">
-        <v>3.809000000000005</v>
+        <v>5.776000000000003</v>
       </c>
       <c r="F29">
-        <v>53.109</v>
+        <v>55.076</v>
       </c>
       <c r="G29">
         <v>72</v>
@@ -3665,28 +3665,28 @@
         <v>40.5</v>
       </c>
       <c r="M29">
-        <v>2.6713827</v>
+        <v>2.7703228</v>
       </c>
       <c r="N29">
-        <v>37.8286173</v>
+        <v>37.7296772</v>
       </c>
       <c r="O29">
-        <v>12.861729882</v>
+        <v>12.828090248</v>
       </c>
       <c r="P29">
-        <v>24.966887418</v>
+        <v>24.901586952</v>
       </c>
       <c r="Q29">
-        <v>30.266887418</v>
+        <v>30.20158695199999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1322265420290088</v>
+        <v>0.1330988645371927</v>
       </c>
       <c r="T29">
-        <v>1.126427570461183</v>
+        <v>1.137796857030839</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>15.16068813352725</v>
+        <v>14.61923498590128</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1051266224667787</v>
+        <v>0.104764409252381</v>
       </c>
       <c r="C30">
-        <v>149.8328306949091</v>
+        <v>148.3968156903661</v>
       </c>
       <c r="D30">
-        <v>132.9088306949091</v>
+        <v>133.4398156903661</v>
       </c>
       <c r="E30">
-        <v>5.776000000000003</v>
+        <v>7.743000000000009</v>
       </c>
       <c r="F30">
-        <v>55.076</v>
+        <v>57.04300000000001</v>
       </c>
       <c r="G30">
         <v>72</v>
@@ -3747,28 +3747,28 @@
         <v>40.5</v>
       </c>
       <c r="M30">
-        <v>2.7703228</v>
+        <v>2.8692629</v>
       </c>
       <c r="N30">
-        <v>37.7296772</v>
+        <v>37.6307371</v>
       </c>
       <c r="O30">
-        <v>12.828090248</v>
+        <v>12.794450614</v>
       </c>
       <c r="P30">
-        <v>24.901586952</v>
+        <v>24.836286486</v>
       </c>
       <c r="Q30">
-        <v>30.20158695199999</v>
+        <v>30.136286486</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1330988645371927</v>
+        <v>0.1339957595103958</v>
       </c>
       <c r="T30">
-        <v>1.137796857030839</v>
+        <v>1.149486405194005</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>14.61923498590128</v>
+        <v>14.1151234346633</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.104764409252381</v>
+        <v>0.1044021960379833</v>
       </c>
       <c r="C31">
-        <v>148.3968156903661</v>
+        <v>146.9650603874961</v>
       </c>
       <c r="D31">
-        <v>133.4398156903661</v>
+        <v>133.9750603874961</v>
       </c>
       <c r="E31">
-        <v>7.742999999999995</v>
+        <v>9.709999999999994</v>
       </c>
       <c r="F31">
-        <v>57.04299999999999</v>
+        <v>59.00999999999999</v>
       </c>
       <c r="G31">
         <v>72</v>
@@ -3829,28 +3829,28 @@
         <v>40.5</v>
       </c>
       <c r="M31">
-        <v>2.869262899999999</v>
+        <v>2.968202999999999</v>
       </c>
       <c r="N31">
-        <v>37.6307371</v>
+        <v>37.531797</v>
       </c>
       <c r="O31">
-        <v>12.794450614</v>
+        <v>12.76081098</v>
       </c>
       <c r="P31">
-        <v>24.836286486</v>
+        <v>24.77098602</v>
       </c>
       <c r="Q31">
-        <v>30.136286486</v>
+        <v>30.07098601999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1339957595103958</v>
+        <v>0.1349182800542619</v>
       </c>
       <c r="T31">
-        <v>1.149486405194005</v>
+        <v>1.161509940447548</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>14.11512343466331</v>
+        <v>13.64461932017453</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1044021960379833</v>
+        <v>0.1040399828235856</v>
       </c>
       <c r="C32">
-        <v>146.9650603874961</v>
+        <v>145.5376162514079</v>
       </c>
       <c r="D32">
-        <v>133.9750603874961</v>
+        <v>134.5146162514079</v>
       </c>
       <c r="E32">
-        <v>9.709999999999994</v>
+        <v>11.677</v>
       </c>
       <c r="F32">
-        <v>59.00999999999999</v>
+        <v>60.977</v>
       </c>
       <c r="G32">
         <v>72</v>
@@ -3911,28 +3911,28 @@
         <v>40.5</v>
       </c>
       <c r="M32">
-        <v>2.968202999999999</v>
+        <v>3.0671431</v>
       </c>
       <c r="N32">
-        <v>37.531797</v>
+        <v>37.4328569</v>
       </c>
       <c r="O32">
-        <v>12.76081098</v>
+        <v>12.727171346</v>
       </c>
       <c r="P32">
-        <v>24.77098602</v>
+        <v>24.705685554</v>
       </c>
       <c r="Q32">
-        <v>30.07098601999999</v>
+        <v>30.005685554</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1349182800542619</v>
+        <v>0.1358675403240371</v>
       </c>
       <c r="T32">
-        <v>1.161509940447548</v>
+        <v>1.17388198396931</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>13.64461932017453</v>
+        <v>13.20447030984632</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1040399828235856</v>
+        <v>0.1039945696091879</v>
       </c>
       <c r="C33">
-        <v>145.5376162514079</v>
+        <v>143.6385709089424</v>
       </c>
       <c r="D33">
-        <v>134.5146162514079</v>
+        <v>134.5825709089424</v>
       </c>
       <c r="E33">
-        <v>11.677</v>
+        <v>13.644</v>
       </c>
       <c r="F33">
-        <v>60.977</v>
+        <v>62.944</v>
       </c>
       <c r="G33">
         <v>72</v>
@@ -3993,45 +3993,45 @@
         <v>40.5</v>
       </c>
       <c r="M33">
-        <v>3.0671431</v>
+        <v>3.260499199999999</v>
       </c>
       <c r="N33">
-        <v>37.4328569</v>
+        <v>37.2395008</v>
       </c>
       <c r="O33">
-        <v>12.727171346</v>
+        <v>12.661430272</v>
       </c>
       <c r="P33">
-        <v>24.705685554</v>
+        <v>24.578070528</v>
       </c>
       <c r="Q33">
-        <v>30.005685554</v>
+        <v>29.87807052799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1358675403240371</v>
+        <v>0.1368447200135116</v>
       </c>
       <c r="T33">
-        <v>1.17388198396931</v>
+        <v>1.186617911124064</v>
       </c>
       <c r="U33">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V33">
         <v>0.34</v>
       </c>
       <c r="W33">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>13.20447030984632</v>
+        <v>12.42141080727761</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1039945696091879</v>
+        <v>0.1036422563947902</v>
       </c>
       <c r="C34">
-        <v>143.6385709089424</v>
+        <v>142.2011010539735</v>
       </c>
       <c r="D34">
-        <v>134.5825709089424</v>
+        <v>135.1121010539735</v>
       </c>
       <c r="E34">
-        <v>13.644</v>
+        <v>15.611</v>
       </c>
       <c r="F34">
-        <v>62.944</v>
+        <v>64.911</v>
       </c>
       <c r="G34">
         <v>72</v>
@@ -4075,28 +4075,28 @@
         <v>40.5</v>
       </c>
       <c r="M34">
-        <v>3.260499199999999</v>
+        <v>3.3623898</v>
       </c>
       <c r="N34">
-        <v>37.2395008</v>
+        <v>37.1376102</v>
       </c>
       <c r="O34">
-        <v>12.661430272</v>
+        <v>12.626787468</v>
       </c>
       <c r="P34">
-        <v>24.578070528</v>
+        <v>24.510822732</v>
       </c>
       <c r="Q34">
-        <v>29.87807052799999</v>
+        <v>29.81082273199999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1368447200135116</v>
+        <v>0.1378510692459555</v>
       </c>
       <c r="T34">
-        <v>1.186617911124064</v>
+        <v>1.199734015208811</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>12.42141080727761</v>
+        <v>12.04500441917829</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1036422563947902</v>
+        <v>0.1032899431803924</v>
       </c>
       <c r="C35">
-        <v>142.2011010539735</v>
+        <v>140.7678146501654</v>
       </c>
       <c r="D35">
-        <v>135.1121010539735</v>
+        <v>135.6458146501654</v>
       </c>
       <c r="E35">
-        <v>15.611</v>
+        <v>17.578</v>
       </c>
       <c r="F35">
-        <v>64.911</v>
+        <v>66.878</v>
       </c>
       <c r="G35">
         <v>72</v>
@@ -4157,28 +4157,28 @@
         <v>40.5</v>
       </c>
       <c r="M35">
-        <v>3.3623898</v>
+        <v>3.4642804</v>
       </c>
       <c r="N35">
-        <v>37.1376102</v>
+        <v>37.0357196</v>
       </c>
       <c r="O35">
-        <v>12.626787468</v>
+        <v>12.592144664</v>
       </c>
       <c r="P35">
-        <v>24.510822732</v>
+        <v>24.443574936</v>
       </c>
       <c r="Q35">
-        <v>29.81082273199999</v>
+        <v>29.74357493599999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1378510692459555</v>
+        <v>0.1388879139096856</v>
       </c>
       <c r="T35">
-        <v>1.199734015208811</v>
+        <v>1.213247576993096</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>12.04500441917829</v>
+        <v>11.6907395833201</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1032899431803924</v>
+        <v>0.1029376299659947</v>
       </c>
       <c r="C36">
-        <v>140.7678146501654</v>
+        <v>139.338761469955</v>
       </c>
       <c r="D36">
-        <v>135.6458146501654</v>
+        <v>136.183761469955</v>
       </c>
       <c r="E36">
-        <v>17.578</v>
+        <v>19.545</v>
       </c>
       <c r="F36">
-        <v>66.878</v>
+        <v>68.845</v>
       </c>
       <c r="G36">
         <v>72</v>
@@ -4239,28 +4239,28 @@
         <v>40.5</v>
       </c>
       <c r="M36">
-        <v>3.4642804</v>
+        <v>3.566171</v>
       </c>
       <c r="N36">
-        <v>37.0357196</v>
+        <v>36.933829</v>
       </c>
       <c r="O36">
-        <v>12.592144664</v>
+        <v>12.55750186</v>
       </c>
       <c r="P36">
-        <v>24.443574936</v>
+        <v>24.37632714</v>
       </c>
       <c r="Q36">
-        <v>29.74357493599999</v>
+        <v>29.67632714</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1388879139096856</v>
+        <v>0.1399566614861458</v>
       </c>
       <c r="T36">
-        <v>1.213247576993096</v>
+        <v>1.227176940678436</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>11.6907395833201</v>
+        <v>11.3567184523681</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1029376299659947</v>
+        <v>0.102585316751597</v>
       </c>
       <c r="C37">
-        <v>139.338761469955</v>
+        <v>137.9139920784767</v>
       </c>
       <c r="D37">
-        <v>136.183761469955</v>
+        <v>136.7259920784767</v>
       </c>
       <c r="E37">
-        <v>19.545</v>
+        <v>21.512</v>
       </c>
       <c r="F37">
-        <v>68.845</v>
+        <v>70.812</v>
       </c>
       <c r="G37">
         <v>72</v>
@@ -4321,28 +4321,28 @@
         <v>40.5</v>
       </c>
       <c r="M37">
-        <v>3.566171</v>
+        <v>3.6680616</v>
       </c>
       <c r="N37">
-        <v>36.933829</v>
+        <v>36.8319384</v>
       </c>
       <c r="O37">
-        <v>12.55750186</v>
+        <v>12.522859056</v>
       </c>
       <c r="P37">
-        <v>24.37632714</v>
+        <v>24.309079344</v>
       </c>
       <c r="Q37">
-        <v>29.67632714</v>
+        <v>29.60907934399999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1399566614861458</v>
+        <v>0.1410588074243704</v>
       </c>
       <c r="T37">
-        <v>1.227176940678436</v>
+        <v>1.241541596978943</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>11.3567184523681</v>
+        <v>11.04125405091343</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.102585316751597</v>
+        <v>0.1022330035371993</v>
       </c>
       <c r="C38">
-        <v>137.9139920784767</v>
+        <v>136.4935578494071</v>
       </c>
       <c r="D38">
-        <v>136.7259920784767</v>
+        <v>137.2725578494071</v>
       </c>
       <c r="E38">
-        <v>21.512</v>
+        <v>23.479</v>
       </c>
       <c r="F38">
-        <v>70.812</v>
+        <v>72.779</v>
       </c>
       <c r="G38">
         <v>72</v>
@@ -4403,28 +4403,28 @@
         <v>40.5</v>
       </c>
       <c r="M38">
-        <v>3.6680616</v>
+        <v>3.7699522</v>
       </c>
       <c r="N38">
-        <v>36.8319384</v>
+        <v>36.7300478</v>
       </c>
       <c r="O38">
-        <v>12.522859056</v>
+        <v>12.488216252</v>
       </c>
       <c r="P38">
-        <v>24.309079344</v>
+        <v>24.241831548</v>
       </c>
       <c r="Q38">
-        <v>29.60907934399999</v>
+        <v>29.541831548</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1410588074243704</v>
+        <v>0.1421959421225386</v>
       </c>
       <c r="T38">
-        <v>1.241541596978942</v>
+        <v>1.256362274114386</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>11.04125405091343</v>
+        <v>10.74284177926712</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1022330035371993</v>
+        <v>0.1018806903228016</v>
       </c>
       <c r="C39">
-        <v>136.4935578494071</v>
+        <v>135.0775109811901</v>
       </c>
       <c r="D39">
-        <v>137.2725578494071</v>
+        <v>137.8235109811901</v>
       </c>
       <c r="E39">
-        <v>23.479</v>
+        <v>25.446</v>
       </c>
       <c r="F39">
-        <v>72.779</v>
+        <v>74.746</v>
       </c>
       <c r="G39">
         <v>72</v>
@@ -4485,28 +4485,28 @@
         <v>40.5</v>
       </c>
       <c r="M39">
-        <v>3.7699522</v>
+        <v>3.8718428</v>
       </c>
       <c r="N39">
-        <v>36.7300478</v>
+        <v>36.6281572</v>
       </c>
       <c r="O39">
-        <v>12.488216252</v>
+        <v>12.453573448</v>
       </c>
       <c r="P39">
-        <v>24.241831548</v>
+        <v>24.174583752</v>
       </c>
       <c r="Q39">
-        <v>29.541831548</v>
+        <v>29.474583752</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1421959421225386</v>
+        <v>0.1433697585851639</v>
       </c>
       <c r="T39">
-        <v>1.256362274114386</v>
+        <v>1.271661037609037</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>10.74284177926712</v>
+        <v>10.46013541665483</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1018806903228016</v>
+        <v>0.1015283771084039</v>
       </c>
       <c r="C40">
-        <v>135.0775109811901</v>
+        <v>133.665904513655</v>
       </c>
       <c r="D40">
-        <v>137.8235109811901</v>
+        <v>138.378904513655</v>
       </c>
       <c r="E40">
-        <v>25.446</v>
+        <v>27.413</v>
       </c>
       <c r="F40">
-        <v>74.746</v>
+        <v>76.71299999999999</v>
       </c>
       <c r="G40">
         <v>72</v>
@@ -4567,28 +4567,28 @@
         <v>40.5</v>
       </c>
       <c r="M40">
-        <v>3.8718428</v>
+        <v>3.9737334</v>
       </c>
       <c r="N40">
-        <v>36.6281572</v>
+        <v>36.5262666</v>
       </c>
       <c r="O40">
-        <v>12.453573448</v>
+        <v>12.418930644</v>
       </c>
       <c r="P40">
-        <v>24.174583752</v>
+        <v>24.107335956</v>
       </c>
       <c r="Q40">
-        <v>29.474583752</v>
+        <v>29.407335956</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1433697585851639</v>
+        <v>0.144582060833449</v>
       </c>
       <c r="T40">
-        <v>1.271661037609037</v>
+        <v>1.287461399906791</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>10.46013541665483</v>
+        <v>10.19192681622778</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1015283771084039</v>
+        <v>0.1011760638940062</v>
       </c>
       <c r="C41">
-        <v>133.665904513655</v>
+        <v>132.2587923450386</v>
       </c>
       <c r="D41">
-        <v>138.378904513655</v>
+        <v>138.9387923450386</v>
       </c>
       <c r="E41">
-        <v>27.413</v>
+        <v>29.38000000000001</v>
       </c>
       <c r="F41">
-        <v>76.71299999999999</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="G41">
         <v>72</v>
@@ -4649,28 +4649,28 @@
         <v>40.5</v>
       </c>
       <c r="M41">
-        <v>3.9737334</v>
+        <v>4.075624</v>
       </c>
       <c r="N41">
-        <v>36.5262666</v>
+        <v>36.424376</v>
       </c>
       <c r="O41">
-        <v>12.418930644</v>
+        <v>12.38428784</v>
       </c>
       <c r="P41">
-        <v>24.107335956</v>
+        <v>24.04008816</v>
       </c>
       <c r="Q41">
-        <v>29.407335956</v>
+        <v>29.34008816</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.144582060833449</v>
+        <v>0.145834773156677</v>
       </c>
       <c r="T41">
-        <v>1.287461399906791</v>
+        <v>1.303788440947804</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>10.19192681622778</v>
+        <v>9.937128645822087</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1011760638940062</v>
+        <v>0.1012837706796085</v>
       </c>
       <c r="C42">
-        <v>132.2587923450386</v>
+        <v>130.1201470386331</v>
       </c>
       <c r="D42">
-        <v>138.9387923450386</v>
+        <v>138.7671470386331</v>
       </c>
       <c r="E42">
-        <v>29.38000000000001</v>
+        <v>31.34700000000001</v>
       </c>
       <c r="F42">
-        <v>78.68000000000001</v>
+        <v>80.64700000000001</v>
       </c>
       <c r="G42">
         <v>72</v>
@@ -4731,45 +4731,45 @@
         <v>40.5</v>
       </c>
       <c r="M42">
-        <v>4.075624</v>
+        <v>4.3146145</v>
       </c>
       <c r="N42">
-        <v>36.424376</v>
+        <v>36.1853855</v>
       </c>
       <c r="O42">
-        <v>12.38428784</v>
+        <v>12.30303107</v>
       </c>
       <c r="P42">
-        <v>24.04008816</v>
+        <v>23.88235443</v>
       </c>
       <c r="Q42">
-        <v>29.34008816</v>
+        <v>29.18235443</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.145834773156677</v>
+        <v>0.1471299503044212</v>
       </c>
       <c r="T42">
-        <v>1.303788440947804</v>
+        <v>1.320668941007157</v>
       </c>
       <c r="U42">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V42">
         <v>0.34</v>
       </c>
       <c r="W42">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>9.937128645822087</v>
+        <v>9.386701871047807</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1012837706796085</v>
+        <v>0.1009426774652108</v>
       </c>
       <c r="C43">
-        <v>130.1201470386331</v>
+        <v>128.6981859823227</v>
       </c>
       <c r="D43">
-        <v>138.7671470386331</v>
+        <v>139.3121859823227</v>
       </c>
       <c r="E43">
-        <v>31.34700000000001</v>
+        <v>33.31400000000001</v>
       </c>
       <c r="F43">
-        <v>80.64700000000001</v>
+        <v>82.614</v>
       </c>
       <c r="G43">
         <v>72</v>
@@ -4813,28 +4813,28 @@
         <v>40.5</v>
       </c>
       <c r="M43">
-        <v>4.3146145</v>
+        <v>4.419849</v>
       </c>
       <c r="N43">
-        <v>36.1853855</v>
+        <v>36.080151</v>
       </c>
       <c r="O43">
-        <v>12.30303107</v>
+        <v>12.26725134</v>
       </c>
       <c r="P43">
-        <v>23.88235443</v>
+        <v>23.81289966</v>
       </c>
       <c r="Q43">
-        <v>29.18235443</v>
+        <v>29.11289966</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1471299503044212</v>
+        <v>0.1484697887331221</v>
       </c>
       <c r="T43">
-        <v>1.320668941007157</v>
+        <v>1.338131527275453</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>9.386701871047807</v>
+        <v>9.163208969356193</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1009426774652108</v>
+        <v>0.1006015842508131</v>
       </c>
       <c r="C44">
-        <v>128.6981859823227</v>
+        <v>127.2805233331808</v>
       </c>
       <c r="D44">
-        <v>139.3121859823227</v>
+        <v>139.8615233331808</v>
       </c>
       <c r="E44">
-        <v>33.31399999999999</v>
+        <v>35.28099999999999</v>
       </c>
       <c r="F44">
-        <v>82.61399999999999</v>
+        <v>84.58099999999999</v>
       </c>
       <c r="G44">
         <v>72</v>
@@ -4895,28 +4895,28 @@
         <v>40.5</v>
       </c>
       <c r="M44">
-        <v>4.419848999999999</v>
+        <v>4.525083499999999</v>
       </c>
       <c r="N44">
-        <v>36.080151</v>
+        <v>35.9749165</v>
       </c>
       <c r="O44">
-        <v>12.26725134</v>
+        <v>12.23147161</v>
       </c>
       <c r="P44">
-        <v>23.81289966</v>
+        <v>23.74344489</v>
       </c>
       <c r="Q44">
-        <v>29.11289966</v>
+        <v>29.04344489</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1484697887331221</v>
+        <v>0.1498566390365142</v>
       </c>
       <c r="T44">
-        <v>1.338131527275453</v>
+        <v>1.356206835868952</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>9.163208969356194</v>
+        <v>8.95011108634791</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1006015842508131</v>
+        <v>0.1002604910364154</v>
       </c>
       <c r="C45">
-        <v>127.2805233331808</v>
+        <v>125.8672101410878</v>
       </c>
       <c r="D45">
-        <v>139.8615233331808</v>
+        <v>140.4152101410878</v>
       </c>
       <c r="E45">
-        <v>35.28099999999999</v>
+        <v>37.248</v>
       </c>
       <c r="F45">
-        <v>84.58099999999999</v>
+        <v>86.548</v>
       </c>
       <c r="G45">
         <v>72</v>
@@ -4977,28 +4977,28 @@
         <v>40.5</v>
       </c>
       <c r="M45">
-        <v>4.525083499999999</v>
+        <v>4.630318</v>
       </c>
       <c r="N45">
-        <v>35.9749165</v>
+        <v>35.869682</v>
       </c>
       <c r="O45">
-        <v>12.23147161</v>
+        <v>12.19569188</v>
       </c>
       <c r="P45">
-        <v>23.74344489</v>
+        <v>23.67399012</v>
       </c>
       <c r="Q45">
-        <v>29.04344489</v>
+        <v>28.97399012</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1498566390365142</v>
+        <v>0.1512930197078846</v>
       </c>
       <c r="T45">
-        <v>1.356206835868952</v>
+        <v>1.374927691197933</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.95011108634791</v>
+        <v>8.746699470749093</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1002604910364154</v>
+        <v>0.09991939782201766</v>
       </c>
       <c r="C46">
-        <v>125.8672101410878</v>
+        <v>124.4582982675264</v>
       </c>
       <c r="D46">
-        <v>140.4152101410878</v>
+        <v>140.9732982675264</v>
       </c>
       <c r="E46">
-        <v>37.248</v>
+        <v>39.215</v>
       </c>
       <c r="F46">
-        <v>86.548</v>
+        <v>88.515</v>
       </c>
       <c r="G46">
         <v>72</v>
@@ -5059,28 +5059,28 @@
         <v>40.5</v>
       </c>
       <c r="M46">
-        <v>4.630318</v>
+        <v>4.7355525</v>
       </c>
       <c r="N46">
-        <v>35.869682</v>
+        <v>35.7644475</v>
       </c>
       <c r="O46">
-        <v>12.19569188</v>
+        <v>12.15991215</v>
       </c>
       <c r="P46">
-        <v>23.67399012</v>
+        <v>23.60453535</v>
       </c>
       <c r="Q46">
-        <v>28.97399012</v>
+        <v>28.90453535</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1512930197078846</v>
+        <v>0.1527816324036685</v>
       </c>
       <c r="T46">
-        <v>1.374927691197933</v>
+        <v>1.394329304902513</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.746699470749093</v>
+        <v>8.552328371399113</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09991939782201766</v>
+        <v>0.09957830460761995</v>
       </c>
       <c r="C47">
-        <v>124.4582982675264</v>
+        <v>123.053840401775</v>
       </c>
       <c r="D47">
-        <v>140.9732982675264</v>
+        <v>141.535840401775</v>
       </c>
       <c r="E47">
-        <v>39.215</v>
+        <v>41.182</v>
       </c>
       <c r="F47">
-        <v>88.515</v>
+        <v>90.482</v>
       </c>
       <c r="G47">
         <v>72</v>
@@ -5141,28 +5141,28 @@
         <v>40.5</v>
       </c>
       <c r="M47">
-        <v>4.7355525</v>
+        <v>4.840787</v>
       </c>
       <c r="N47">
-        <v>35.7644475</v>
+        <v>35.659213</v>
       </c>
       <c r="O47">
-        <v>12.15991215</v>
+        <v>12.12413242</v>
       </c>
       <c r="P47">
-        <v>23.60453535</v>
+        <v>23.53508058</v>
       </c>
       <c r="Q47">
-        <v>28.90453535</v>
+        <v>28.83508058</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1527816324036685</v>
+        <v>0.1543253789029999</v>
       </c>
       <c r="T47">
-        <v>1.394329304902513</v>
+        <v>1.414449496892448</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>8.552328371399113</v>
+        <v>8.366408189412176</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09957830460761995</v>
+        <v>0.09923721139322225</v>
       </c>
       <c r="C48">
-        <v>123.053840401775</v>
+        <v>121.6538900774901</v>
       </c>
       <c r="D48">
-        <v>141.535840401775</v>
+        <v>142.1028900774901</v>
       </c>
       <c r="E48">
-        <v>41.182</v>
+        <v>43.149</v>
       </c>
       <c r="F48">
-        <v>90.482</v>
+        <v>92.449</v>
       </c>
       <c r="G48">
         <v>72</v>
@@ -5223,28 +5223,28 @@
         <v>40.5</v>
       </c>
       <c r="M48">
-        <v>4.840787</v>
+        <v>4.9460215</v>
       </c>
       <c r="N48">
-        <v>35.659213</v>
+        <v>35.5539785</v>
       </c>
       <c r="O48">
-        <v>12.12413242</v>
+        <v>12.08835269</v>
       </c>
       <c r="P48">
-        <v>23.53508058</v>
+        <v>23.46562581</v>
       </c>
       <c r="Q48">
-        <v>28.83508058</v>
+        <v>28.76562581</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1543253789029999</v>
+        <v>0.1559273799872118</v>
       </c>
       <c r="T48">
-        <v>1.414449496892448</v>
+        <v>1.435328941410306</v>
       </c>
       <c r="U48">
         <v>0.0535</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>8.366408189412176</v>
+        <v>8.188399504531066</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09923721139322225</v>
+        <v>0.09889611817882454</v>
       </c>
       <c r="C49">
-        <v>121.6538900774901</v>
+        <v>120.2585016896888</v>
       </c>
       <c r="D49">
-        <v>142.1028900774901</v>
+        <v>142.6745016896888</v>
       </c>
       <c r="E49">
-        <v>43.149</v>
+        <v>45.116</v>
       </c>
       <c r="F49">
-        <v>92.449</v>
+        <v>94.416</v>
       </c>
       <c r="G49">
         <v>72</v>
@@ -5305,28 +5305,28 @@
         <v>40.5</v>
       </c>
       <c r="M49">
-        <v>4.9460215</v>
+        <v>5.051256</v>
       </c>
       <c r="N49">
-        <v>35.5539785</v>
+        <v>35.448744</v>
       </c>
       <c r="O49">
-        <v>12.08835269</v>
+        <v>12.05257296</v>
       </c>
       <c r="P49">
-        <v>23.46562581</v>
+        <v>23.39617104</v>
       </c>
       <c r="Q49">
-        <v>28.76562581</v>
+        <v>28.69617104</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1559273799872118</v>
+        <v>0.1575909964977395</v>
       </c>
       <c r="T49">
-        <v>1.435328941410306</v>
+        <v>1.457011441486542</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>8.188399504531066</v>
+        <v>8.017807848186669</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09889611817882453</v>
+        <v>0.09855502496442682</v>
       </c>
       <c r="C50">
-        <v>120.2585016896888</v>
+        <v>118.8677305121429</v>
       </c>
       <c r="D50">
-        <v>142.6745016896888</v>
+        <v>143.2507305121429</v>
       </c>
       <c r="E50">
-        <v>45.116</v>
+        <v>47.083</v>
       </c>
       <c r="F50">
-        <v>94.416</v>
+        <v>96.383</v>
       </c>
       <c r="G50">
         <v>72</v>
@@ -5387,28 +5387,28 @@
         <v>40.5</v>
       </c>
       <c r="M50">
-        <v>5.051256</v>
+        <v>5.156490499999999</v>
       </c>
       <c r="N50">
-        <v>35.448744</v>
+        <v>35.3435095</v>
       </c>
       <c r="O50">
-        <v>12.05257296</v>
+        <v>12.01679323</v>
       </c>
       <c r="P50">
-        <v>23.39617104</v>
+        <v>23.32671627</v>
       </c>
       <c r="Q50">
-        <v>28.69617104</v>
+        <v>28.62671627</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1575909964977395</v>
+        <v>0.1593198528714251</v>
       </c>
       <c r="T50">
-        <v>1.457011441486542</v>
+        <v>1.479544235683415</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>8.017807848186669</v>
+        <v>7.854179116591024</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09855502496442682</v>
+        <v>0.0982139317500291</v>
       </c>
       <c r="C51">
-        <v>118.8677305121429</v>
+        <v>117.4816327151967</v>
       </c>
       <c r="D51">
-        <v>143.2507305121429</v>
+        <v>143.8316327151967</v>
       </c>
       <c r="E51">
-        <v>47.083</v>
+        <v>49.05</v>
       </c>
       <c r="F51">
-        <v>96.383</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="G51">
         <v>72</v>
@@ -5469,28 +5469,28 @@
         <v>40.5</v>
       </c>
       <c r="M51">
-        <v>5.156490499999999</v>
+        <v>5.261724999999999</v>
       </c>
       <c r="N51">
-        <v>35.3435095</v>
+        <v>35.238275</v>
       </c>
       <c r="O51">
-        <v>12.01679323</v>
+        <v>11.9810135</v>
       </c>
       <c r="P51">
-        <v>23.32671627</v>
+        <v>23.2572615</v>
       </c>
       <c r="Q51">
-        <v>28.62671627</v>
+        <v>28.5572615</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1593198528714251</v>
+        <v>0.1611178635000582</v>
       </c>
       <c r="T51">
-        <v>1.479544235683415</v>
+        <v>1.502978341648163</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.854179116591024</v>
+        <v>7.697095534259203</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0982139317500291</v>
+        <v>0.09814211853563139</v>
       </c>
       <c r="C52">
-        <v>117.4816327151967</v>
+        <v>115.6375358098164</v>
       </c>
       <c r="D52">
-        <v>143.8316327151967</v>
+        <v>143.9545358098164</v>
       </c>
       <c r="E52">
-        <v>49.05</v>
+        <v>51.017</v>
       </c>
       <c r="F52">
-        <v>98.34999999999999</v>
+        <v>100.317</v>
       </c>
       <c r="G52">
         <v>72</v>
@@ -5551,45 +5551,45 @@
         <v>40.5</v>
       </c>
       <c r="M52">
-        <v>5.261724999999999</v>
+        <v>5.4472131</v>
       </c>
       <c r="N52">
-        <v>35.238275</v>
+        <v>35.0527869</v>
       </c>
       <c r="O52">
-        <v>11.9810135</v>
+        <v>11.917947546</v>
       </c>
       <c r="P52">
-        <v>23.2572615</v>
+        <v>23.134839354</v>
       </c>
       <c r="Q52">
-        <v>28.5572615</v>
+        <v>28.434839354</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1611178635000582</v>
+        <v>0.1629892623176151</v>
       </c>
       <c r="T52">
-        <v>1.502978341648163</v>
+        <v>1.527368941733922</v>
       </c>
       <c r="U52">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V52">
         <v>0.34</v>
       </c>
       <c r="W52">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y52">
-        <v>7.697095534259203</v>
+        <v>7.434994603020029</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09814211853563139</v>
+        <v>0.09780630532123369</v>
       </c>
       <c r="C53">
-        <v>115.6375358098164</v>
+        <v>114.2480544407177</v>
       </c>
       <c r="D53">
-        <v>143.9545358098164</v>
+        <v>144.5320544407177</v>
       </c>
       <c r="E53">
-        <v>51.017</v>
+        <v>52.98399999999999</v>
       </c>
       <c r="F53">
-        <v>100.317</v>
+        <v>102.284</v>
       </c>
       <c r="G53">
         <v>72</v>
@@ -5633,28 +5633,28 @@
         <v>40.5</v>
       </c>
       <c r="M53">
-        <v>5.4472131</v>
+        <v>5.554021199999999</v>
       </c>
       <c r="N53">
-        <v>35.0527869</v>
+        <v>34.9459788</v>
       </c>
       <c r="O53">
-        <v>11.917947546</v>
+        <v>11.881632792</v>
       </c>
       <c r="P53">
-        <v>23.134839354</v>
+        <v>23.064346008</v>
       </c>
       <c r="Q53">
-        <v>28.434839354</v>
+        <v>28.36434600799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1629892623176151</v>
+        <v>0.1649386360859035</v>
       </c>
       <c r="T53">
-        <v>1.527368941733922</v>
+        <v>1.552775816823253</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>7.434994603020029</v>
+        <v>7.292013937577337</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09780630532123369</v>
+        <v>0.09747049210683598</v>
       </c>
       <c r="C54">
-        <v>114.2480544407177</v>
+        <v>112.8632255295317</v>
       </c>
       <c r="D54">
-        <v>144.5320544407177</v>
+        <v>145.1142255295317</v>
       </c>
       <c r="E54">
-        <v>52.98399999999999</v>
+        <v>54.95100000000001</v>
       </c>
       <c r="F54">
-        <v>102.284</v>
+        <v>104.251</v>
       </c>
       <c r="G54">
         <v>72</v>
@@ -5715,28 +5715,28 @@
         <v>40.5</v>
       </c>
       <c r="M54">
-        <v>5.554021199999999</v>
+        <v>5.660829300000001</v>
       </c>
       <c r="N54">
-        <v>34.9459788</v>
+        <v>34.8391707</v>
       </c>
       <c r="O54">
-        <v>11.881632792</v>
+        <v>11.845318038</v>
       </c>
       <c r="P54">
-        <v>23.064346008</v>
+        <v>22.99385266199999</v>
       </c>
       <c r="Q54">
-        <v>28.36434600799999</v>
+        <v>28.29385266199999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1649386360859035</v>
+        <v>0.1669709619294382</v>
       </c>
       <c r="T54">
-        <v>1.552775816823253</v>
+        <v>1.579263835533407</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>7.292013937577337</v>
+        <v>7.1544287689438</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09747049210683598</v>
+        <v>0.09713467889243826</v>
       </c>
       <c r="C55">
-        <v>112.8632255295317</v>
+        <v>111.4831055235391</v>
       </c>
       <c r="D55">
-        <v>145.1142255295317</v>
+        <v>145.7011055235391</v>
       </c>
       <c r="E55">
-        <v>54.95100000000001</v>
+        <v>56.91800000000001</v>
       </c>
       <c r="F55">
-        <v>104.251</v>
+        <v>106.218</v>
       </c>
       <c r="G55">
         <v>72</v>
@@ -5797,28 +5797,28 @@
         <v>40.5</v>
       </c>
       <c r="M55">
-        <v>5.660829300000001</v>
+        <v>5.7676374</v>
       </c>
       <c r="N55">
-        <v>34.8391707</v>
+        <v>34.7323626</v>
       </c>
       <c r="O55">
-        <v>11.845318038</v>
+        <v>11.809003284</v>
       </c>
       <c r="P55">
-        <v>22.99385266199999</v>
+        <v>22.923359316</v>
       </c>
       <c r="Q55">
-        <v>28.29385266199999</v>
+        <v>28.223359316</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1669709619294382</v>
+        <v>0.1690916497661702</v>
       </c>
       <c r="T55">
-        <v>1.579263835533407</v>
+        <v>1.60690350723096</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>7.1544287689438</v>
+        <v>7.021939347296694</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09713467889243826</v>
+        <v>0.09679886567804055</v>
       </c>
       <c r="C56">
-        <v>111.4831055235391</v>
+        <v>110.107751786879</v>
       </c>
       <c r="D56">
-        <v>145.7011055235391</v>
+        <v>146.292751786879</v>
       </c>
       <c r="E56">
-        <v>56.91800000000001</v>
+        <v>58.88500000000001</v>
       </c>
       <c r="F56">
-        <v>106.218</v>
+        <v>108.185</v>
       </c>
       <c r="G56">
         <v>72</v>
@@ -5879,28 +5879,28 @@
         <v>40.5</v>
       </c>
       <c r="M56">
-        <v>5.7676374</v>
+        <v>5.8744455</v>
       </c>
       <c r="N56">
-        <v>34.7323626</v>
+        <v>34.6255545</v>
       </c>
       <c r="O56">
-        <v>11.809003284</v>
+        <v>11.77268853</v>
       </c>
       <c r="P56">
-        <v>22.923359316</v>
+        <v>22.85286597</v>
       </c>
       <c r="Q56">
-        <v>28.223359316</v>
+        <v>28.15286597</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1690916497661702</v>
+        <v>0.1713065903956457</v>
       </c>
       <c r="T56">
-        <v>1.60690350723096</v>
+        <v>1.635771608781736</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>7.021939347296694</v>
+        <v>6.89426772280039</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09679886567804055</v>
+        <v>0.09646305246364284</v>
       </c>
       <c r="C57">
-        <v>110.107751786879</v>
+        <v>108.7372226192402</v>
       </c>
       <c r="D57">
-        <v>146.292751786879</v>
+        <v>146.8892226192402</v>
       </c>
       <c r="E57">
-        <v>58.88500000000001</v>
+        <v>60.852</v>
       </c>
       <c r="F57">
-        <v>108.185</v>
+        <v>110.152</v>
       </c>
       <c r="G57">
         <v>72</v>
@@ -5961,28 +5961,28 @@
         <v>40.5</v>
       </c>
       <c r="M57">
-        <v>5.8744455</v>
+        <v>5.981253600000001</v>
       </c>
       <c r="N57">
-        <v>34.6255545</v>
+        <v>34.5187464</v>
       </c>
       <c r="O57">
-        <v>11.77268853</v>
+        <v>11.736373776</v>
       </c>
       <c r="P57">
-        <v>22.85286597</v>
+        <v>22.782372624</v>
       </c>
       <c r="Q57">
-        <v>28.15286597</v>
+        <v>28.08237262399999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1713065903956457</v>
+        <v>0.1736222101446429</v>
       </c>
       <c r="T57">
-        <v>1.635771608781736</v>
+        <v>1.665951896766639</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.89426772280039</v>
+        <v>6.771155799178953</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09646305246364284</v>
+        <v>0.09612723924924514</v>
       </c>
       <c r="C58">
-        <v>108.7372226192402</v>
+        <v>107.3715772750117</v>
       </c>
       <c r="D58">
-        <v>146.8892226192402</v>
+        <v>147.4905772750117</v>
       </c>
       <c r="E58">
-        <v>60.852</v>
+        <v>62.819</v>
       </c>
       <c r="F58">
-        <v>110.152</v>
+        <v>112.119</v>
       </c>
       <c r="G58">
         <v>72</v>
@@ -6043,28 +6043,28 @@
         <v>40.5</v>
       </c>
       <c r="M58">
-        <v>5.981253600000001</v>
+        <v>6.0880617</v>
       </c>
       <c r="N58">
-        <v>34.5187464</v>
+        <v>34.4119383</v>
       </c>
       <c r="O58">
-        <v>11.736373776</v>
+        <v>11.700059022</v>
       </c>
       <c r="P58">
-        <v>22.782372624</v>
+        <v>22.711879278</v>
       </c>
       <c r="Q58">
-        <v>28.08237262399999</v>
+        <v>28.011879278</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1736222101446429</v>
+        <v>0.1760455331377794</v>
       </c>
       <c r="T58">
-        <v>1.665951896766639</v>
+        <v>1.697535919076421</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.771155799178953</v>
+        <v>6.652363592175815</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09612723924924514</v>
+        <v>0.09579142603484742</v>
       </c>
       <c r="C59">
-        <v>107.3715772750117</v>
+        <v>106.0108759829052</v>
       </c>
       <c r="D59">
-        <v>147.4905772750117</v>
+        <v>148.0968759829052</v>
       </c>
       <c r="E59">
-        <v>62.819</v>
+        <v>64.78600000000002</v>
       </c>
       <c r="F59">
-        <v>112.119</v>
+        <v>114.086</v>
       </c>
       <c r="G59">
         <v>72</v>
@@ -6125,28 +6125,28 @@
         <v>40.5</v>
       </c>
       <c r="M59">
-        <v>6.0880617</v>
+        <v>6.194869800000001</v>
       </c>
       <c r="N59">
-        <v>34.4119383</v>
+        <v>34.3051302</v>
       </c>
       <c r="O59">
-        <v>11.700059022</v>
+        <v>11.663744268</v>
       </c>
       <c r="P59">
-        <v>22.711879278</v>
+        <v>22.641385932</v>
       </c>
       <c r="Q59">
-        <v>28.011879278</v>
+        <v>27.941385932</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1760455331377794</v>
+        <v>0.1785842524639225</v>
       </c>
       <c r="T59">
-        <v>1.697535919076421</v>
+        <v>1.730623942448574</v>
       </c>
       <c r="U59">
         <v>0.0543</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>6.652363592175815</v>
+        <v>6.537667668172783</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09579142603484743</v>
+        <v>0.09545561282044973</v>
       </c>
       <c r="C60">
-        <v>106.0108759829052</v>
+        <v>104.6551799660642</v>
       </c>
       <c r="D60">
-        <v>148.0968759829052</v>
+        <v>148.7081799660641</v>
       </c>
       <c r="E60">
-        <v>64.78599999999999</v>
+        <v>66.75299999999999</v>
       </c>
       <c r="F60">
-        <v>114.086</v>
+        <v>116.053</v>
       </c>
       <c r="G60">
         <v>72</v>
@@ -6207,28 +6207,28 @@
         <v>40.5</v>
       </c>
       <c r="M60">
-        <v>6.194869799999999</v>
+        <v>6.3016779</v>
       </c>
       <c r="N60">
-        <v>34.3051302</v>
+        <v>34.1983221</v>
       </c>
       <c r="O60">
-        <v>11.663744268</v>
+        <v>11.627429514</v>
       </c>
       <c r="P60">
-        <v>22.641385932</v>
+        <v>22.570892586</v>
       </c>
       <c r="Q60">
-        <v>27.941385932</v>
+        <v>27.870892586</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1785842524639225</v>
+        <v>0.1812468117571945</v>
       </c>
       <c r="T60">
-        <v>1.730623942448574</v>
+        <v>1.765326015741319</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>6.537667668172785</v>
+        <v>6.426859741593584</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09545561282044973</v>
+        <v>0.09511979960605202</v>
       </c>
       <c r="C61">
-        <v>104.6551799660642</v>
+        <v>103.3045514626722</v>
       </c>
       <c r="D61">
-        <v>148.7081799660641</v>
+        <v>149.3245514626721</v>
       </c>
       <c r="E61">
-        <v>66.75299999999999</v>
+        <v>68.71999999999998</v>
       </c>
       <c r="F61">
-        <v>116.053</v>
+        <v>118.02</v>
       </c>
       <c r="G61">
         <v>72</v>
@@ -6289,28 +6289,28 @@
         <v>40.5</v>
       </c>
       <c r="M61">
-        <v>6.3016779</v>
+        <v>6.408485999999999</v>
       </c>
       <c r="N61">
-        <v>34.1983221</v>
+        <v>34.091514</v>
       </c>
       <c r="O61">
-        <v>11.627429514</v>
+        <v>11.59111476</v>
       </c>
       <c r="P61">
-        <v>22.570892586</v>
+        <v>22.50039924</v>
       </c>
       <c r="Q61">
-        <v>27.870892586</v>
+        <v>27.80039924</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1812468117571945</v>
+        <v>0.18404249901513</v>
       </c>
       <c r="T61">
-        <v>1.765326015741319</v>
+        <v>1.801763192698702</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>6.426859741593584</v>
+        <v>6.319745412567026</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09511979960605202</v>
+        <v>0.09478398639165432</v>
       </c>
       <c r="C62">
-        <v>103.3045514626722</v>
+        <v>101.9590537470766</v>
       </c>
       <c r="D62">
-        <v>149.3245514626721</v>
+        <v>149.9460537470766</v>
       </c>
       <c r="E62">
-        <v>68.71999999999998</v>
+        <v>70.687</v>
       </c>
       <c r="F62">
-        <v>118.02</v>
+        <v>119.987</v>
       </c>
       <c r="G62">
         <v>72</v>
@@ -6371,28 +6371,28 @@
         <v>40.5</v>
       </c>
       <c r="M62">
-        <v>6.408485999999999</v>
+        <v>6.5152941</v>
       </c>
       <c r="N62">
-        <v>34.091514</v>
+        <v>33.9847059</v>
       </c>
       <c r="O62">
-        <v>11.59111476</v>
+        <v>11.554800006</v>
       </c>
       <c r="P62">
-        <v>22.50039924</v>
+        <v>22.429905894</v>
       </c>
       <c r="Q62">
-        <v>27.80039924</v>
+        <v>27.729905894</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.18404249901513</v>
+        <v>0.1869815548503957</v>
       </c>
       <c r="T62">
-        <v>1.801763192698702</v>
+        <v>1.840068942833387</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>6.319745412567026</v>
+        <v>6.21614302875445</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09478398639165432</v>
+        <v>0.09444817317725659</v>
       </c>
       <c r="C63">
-        <v>101.9590537470766</v>
+        <v>100.6187511514421</v>
       </c>
       <c r="D63">
-        <v>149.9460537470766</v>
+        <v>150.5727511514421</v>
       </c>
       <c r="E63">
-        <v>70.687</v>
+        <v>72.654</v>
       </c>
       <c r="F63">
-        <v>119.987</v>
+        <v>121.954</v>
       </c>
       <c r="G63">
         <v>72</v>
@@ -6453,28 +6453,28 @@
         <v>40.5</v>
       </c>
       <c r="M63">
-        <v>6.5152941</v>
+        <v>6.6221022</v>
       </c>
       <c r="N63">
-        <v>33.9847059</v>
+        <v>33.8778978</v>
       </c>
       <c r="O63">
-        <v>11.554800006</v>
+        <v>11.518485252</v>
       </c>
       <c r="P63">
-        <v>22.429905894</v>
+        <v>22.359412548</v>
       </c>
       <c r="Q63">
-        <v>27.729905894</v>
+        <v>27.659412548</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1869815548503957</v>
+        <v>0.1900752978348858</v>
       </c>
       <c r="T63">
-        <v>1.840068942833387</v>
+        <v>1.880390785080423</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>6.21614302875445</v>
+        <v>6.115882657322927</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09444817317725659</v>
+        <v>0.09452815996285889</v>
       </c>
       <c r="C64">
-        <v>100.6187511514421</v>
+        <v>98.50200434255382</v>
       </c>
       <c r="D64">
-        <v>150.5727511514421</v>
+        <v>150.4230043425538</v>
       </c>
       <c r="E64">
-        <v>72.654</v>
+        <v>74.621</v>
       </c>
       <c r="F64">
-        <v>121.954</v>
+        <v>123.921</v>
       </c>
       <c r="G64">
         <v>72</v>
@@ -6535,45 +6535,45 @@
         <v>40.5</v>
       </c>
       <c r="M64">
-        <v>6.6221022</v>
+        <v>6.8528313</v>
       </c>
       <c r="N64">
-        <v>33.8778978</v>
+        <v>33.6471687</v>
       </c>
       <c r="O64">
-        <v>11.518485252</v>
+        <v>11.440037358</v>
       </c>
       <c r="P64">
-        <v>22.359412548</v>
+        <v>22.207131342</v>
       </c>
       <c r="Q64">
-        <v>27.659412548</v>
+        <v>27.507131342</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1900752978348858</v>
+        <v>0.1933362701698889</v>
       </c>
       <c r="T64">
-        <v>1.880390785080423</v>
+        <v>1.922892186367839</v>
       </c>
       <c r="U64">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V64">
         <v>0.34</v>
       </c>
       <c r="W64">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>6.115882657322927</v>
+        <v>5.90996600193558</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09452815996285889</v>
+        <v>0.09419894674846119</v>
       </c>
       <c r="C65">
-        <v>98.50200434255382</v>
+        <v>97.15325672141357</v>
       </c>
       <c r="D65">
-        <v>150.4230043425538</v>
+        <v>151.0412567214136</v>
       </c>
       <c r="E65">
-        <v>74.621</v>
+        <v>76.58799999999999</v>
       </c>
       <c r="F65">
-        <v>123.921</v>
+        <v>125.888</v>
       </c>
       <c r="G65">
         <v>72</v>
@@ -6617,28 +6617,28 @@
         <v>40.5</v>
       </c>
       <c r="M65">
-        <v>6.8528313</v>
+        <v>6.9616064</v>
       </c>
       <c r="N65">
-        <v>33.6471687</v>
+        <v>33.5383936</v>
       </c>
       <c r="O65">
-        <v>11.440037358</v>
+        <v>11.403053824</v>
       </c>
       <c r="P65">
-        <v>22.207131342</v>
+        <v>22.135339776</v>
       </c>
       <c r="Q65">
-        <v>27.507131342</v>
+        <v>27.435339776</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1933362701698889</v>
+        <v>0.1967784076346144</v>
       </c>
       <c r="T65">
-        <v>1.922892186367839</v>
+        <v>1.967754776615668</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.90996600193558</v>
+        <v>5.817622783155336</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09419894674846119</v>
+        <v>0.09386973353406347</v>
       </c>
       <c r="C66">
-        <v>97.15325672141357</v>
+        <v>95.8096122228239</v>
       </c>
       <c r="D66">
-        <v>151.0412567214136</v>
+        <v>151.6646122228239</v>
       </c>
       <c r="E66">
-        <v>76.58799999999999</v>
+        <v>78.55500000000001</v>
       </c>
       <c r="F66">
-        <v>125.888</v>
+        <v>127.855</v>
       </c>
       <c r="G66">
         <v>72</v>
@@ -6699,28 +6699,28 @@
         <v>40.5</v>
       </c>
       <c r="M66">
-        <v>6.9616064</v>
+        <v>7.070381500000001</v>
       </c>
       <c r="N66">
-        <v>33.5383936</v>
+        <v>33.4296185</v>
       </c>
       <c r="O66">
-        <v>11.403053824</v>
+        <v>11.36607029</v>
       </c>
       <c r="P66">
-        <v>22.135339776</v>
+        <v>22.06354821</v>
       </c>
       <c r="Q66">
-        <v>27.435339776</v>
+        <v>27.36354820999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1967784076346144</v>
+        <v>0.2004172386687528</v>
       </c>
       <c r="T66">
-        <v>1.967754776615668</v>
+        <v>2.015180943449087</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.817622783155336</v>
+        <v>5.728120894183714</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09386973353406347</v>
+        <v>0.09354052031966575</v>
       </c>
       <c r="C67">
-        <v>95.8096122228239</v>
+        <v>94.47113429121848</v>
       </c>
       <c r="D67">
-        <v>151.6646122228239</v>
+        <v>152.2931342912185</v>
       </c>
       <c r="E67">
-        <v>78.55500000000001</v>
+        <v>80.52200000000001</v>
       </c>
       <c r="F67">
-        <v>127.855</v>
+        <v>129.822</v>
       </c>
       <c r="G67">
         <v>72</v>
@@ -6781,28 +6781,28 @@
         <v>40.5</v>
       </c>
       <c r="M67">
-        <v>7.070381500000001</v>
+        <v>7.179156600000001</v>
       </c>
       <c r="N67">
-        <v>33.4296185</v>
+        <v>33.3208434</v>
       </c>
       <c r="O67">
-        <v>11.36607029</v>
+        <v>11.329086756</v>
       </c>
       <c r="P67">
-        <v>22.06354821</v>
+        <v>21.991756644</v>
       </c>
       <c r="Q67">
-        <v>27.36354820999999</v>
+        <v>27.291756644</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2004172386687528</v>
+        <v>0.2042701185872522</v>
       </c>
       <c r="T67">
-        <v>2.015180943449087</v>
+        <v>2.065396884802118</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.728120894183714</v>
+        <v>5.64133118366578</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09354052031966575</v>
+        <v>0.09321130710526804</v>
       </c>
       <c r="C68">
-        <v>94.47113429121848</v>
+        <v>93.13788742710238</v>
       </c>
       <c r="D68">
-        <v>152.2931342912185</v>
+        <v>152.9268874271024</v>
       </c>
       <c r="E68">
-        <v>80.52200000000001</v>
+        <v>82.48899999999999</v>
       </c>
       <c r="F68">
-        <v>129.822</v>
+        <v>131.789</v>
       </c>
       <c r="G68">
         <v>72</v>
@@ -6863,28 +6863,28 @@
         <v>40.5</v>
       </c>
       <c r="M68">
-        <v>7.179156600000001</v>
+        <v>7.2879317</v>
       </c>
       <c r="N68">
-        <v>33.3208434</v>
+        <v>33.2120683</v>
       </c>
       <c r="O68">
-        <v>11.329086756</v>
+        <v>11.292103222</v>
       </c>
       <c r="P68">
-        <v>21.991756644</v>
+        <v>21.919965078</v>
       </c>
       <c r="Q68">
-        <v>27.291756644</v>
+        <v>27.21996507799999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2042701185872522</v>
+        <v>0.2083565063796002</v>
       </c>
       <c r="T68">
-        <v>2.065396884802118</v>
+        <v>2.118656216540182</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.64133118366578</v>
+        <v>5.557132210775246</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09321130710526804</v>
+        <v>0.09288209389087032</v>
       </c>
       <c r="C69">
-        <v>93.13788742710238</v>
+        <v>91.80993720911763</v>
       </c>
       <c r="D69">
-        <v>152.9268874271024</v>
+        <v>153.5659372091176</v>
       </c>
       <c r="E69">
-        <v>82.48899999999999</v>
+        <v>84.456</v>
       </c>
       <c r="F69">
-        <v>131.789</v>
+        <v>133.756</v>
       </c>
       <c r="G69">
         <v>72</v>
@@ -6945,28 +6945,28 @@
         <v>40.5</v>
       </c>
       <c r="M69">
-        <v>7.2879317</v>
+        <v>7.3967068</v>
       </c>
       <c r="N69">
-        <v>33.2120683</v>
+        <v>33.1032932</v>
       </c>
       <c r="O69">
-        <v>11.292103222</v>
+        <v>11.255119688</v>
       </c>
       <c r="P69">
-        <v>21.919965078</v>
+        <v>21.848173512</v>
       </c>
       <c r="Q69">
-        <v>27.21996507799999</v>
+        <v>27.14817351199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2083565063796002</v>
+        <v>0.2126982934089698</v>
       </c>
       <c r="T69">
-        <v>2.118656216540182</v>
+        <v>2.175244256511875</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.557132210775246</v>
+        <v>5.475409678263845</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09288209389087032</v>
+        <v>0.09255288067647263</v>
       </c>
       <c r="C70">
-        <v>91.80993720911763</v>
+        <v>90.48735031666439</v>
       </c>
       <c r="D70">
-        <v>153.5659372091176</v>
+        <v>154.2103503166644</v>
       </c>
       <c r="E70">
-        <v>84.456</v>
+        <v>86.42300000000002</v>
       </c>
       <c r="F70">
-        <v>133.756</v>
+        <v>135.723</v>
       </c>
       <c r="G70">
         <v>72</v>
@@ -7027,28 +7027,28 @@
         <v>40.5</v>
       </c>
       <c r="M70">
-        <v>7.3967068</v>
+        <v>7.505481900000001</v>
       </c>
       <c r="N70">
-        <v>33.1032932</v>
+        <v>32.9945181</v>
       </c>
       <c r="O70">
-        <v>11.255119688</v>
+        <v>11.218136154</v>
       </c>
       <c r="P70">
-        <v>21.848173512</v>
+        <v>21.776381946</v>
       </c>
       <c r="Q70">
-        <v>27.14817351199999</v>
+        <v>27.076381946</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2126982934089698</v>
+        <v>0.2173201957305569</v>
       </c>
       <c r="T70">
-        <v>2.175244256511875</v>
+        <v>2.235483137772065</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.475409678263845</v>
+        <v>5.396055914810746</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09255288067647263</v>
+        <v>0.09222366746207492</v>
       </c>
       <c r="C71">
-        <v>90.48735031666439</v>
+        <v>89.17019455309406</v>
       </c>
       <c r="D71">
-        <v>154.2103503166644</v>
+        <v>154.8601945530941</v>
       </c>
       <c r="E71">
-        <v>86.42300000000002</v>
+        <v>88.39</v>
       </c>
       <c r="F71">
-        <v>135.723</v>
+        <v>137.69</v>
       </c>
       <c r="G71">
         <v>72</v>
@@ -7109,28 +7109,28 @@
         <v>40.5</v>
       </c>
       <c r="M71">
-        <v>7.505481900000001</v>
+        <v>7.614257</v>
       </c>
       <c r="N71">
-        <v>32.9945181</v>
+        <v>32.885743</v>
       </c>
       <c r="O71">
-        <v>11.218136154</v>
+        <v>11.18115262</v>
       </c>
       <c r="P71">
-        <v>21.776381946</v>
+        <v>21.70459038</v>
       </c>
       <c r="Q71">
-        <v>27.076381946</v>
+        <v>27.00459038</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2173201957305569</v>
+        <v>0.2222502248735831</v>
       </c>
       <c r="T71">
-        <v>2.235483137772065</v>
+        <v>2.2997379444496</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>5.396055914810746</v>
+        <v>5.318969401742021</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09222366746207492</v>
+        <v>0.0918944542476772</v>
       </c>
       <c r="C72">
-        <v>89.17019455309406</v>
+        <v>87.8585388694909</v>
       </c>
       <c r="D72">
-        <v>154.8601945530941</v>
+        <v>155.5155388694909</v>
       </c>
       <c r="E72">
-        <v>88.39</v>
+        <v>90.35700000000001</v>
       </c>
       <c r="F72">
-        <v>137.69</v>
+        <v>139.657</v>
       </c>
       <c r="G72">
         <v>72</v>
@@ -7191,28 +7191,28 @@
         <v>40.5</v>
       </c>
       <c r="M72">
-        <v>7.614257</v>
+        <v>7.723032100000001</v>
       </c>
       <c r="N72">
-        <v>32.885743</v>
+        <v>32.7769679</v>
       </c>
       <c r="O72">
-        <v>11.18115262</v>
+        <v>11.144169086</v>
       </c>
       <c r="P72">
-        <v>21.70459038</v>
+        <v>21.632798814</v>
       </c>
       <c r="Q72">
-        <v>27.00459038</v>
+        <v>26.932798814</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2222502248735831</v>
+        <v>0.2275202560264732</v>
       </c>
       <c r="T72">
-        <v>2.2997379444496</v>
+        <v>2.368424117104896</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>5.318969401742021</v>
+        <v>5.244054339745655</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09189445424767721</v>
+        <v>0.0915652410332795</v>
       </c>
       <c r="C73">
-        <v>87.8585388694909</v>
+        <v>86.55245338906064</v>
       </c>
       <c r="D73">
-        <v>155.5155388694909</v>
+        <v>156.1764533890606</v>
       </c>
       <c r="E73">
-        <v>90.35699999999999</v>
+        <v>92.324</v>
       </c>
       <c r="F73">
-        <v>139.657</v>
+        <v>141.624</v>
       </c>
       <c r="G73">
         <v>72</v>
@@ -7273,28 +7273,28 @@
         <v>40.5</v>
       </c>
       <c r="M73">
-        <v>7.723032099999999</v>
+        <v>7.8318072</v>
       </c>
       <c r="N73">
-        <v>32.7769679</v>
+        <v>32.6681928</v>
       </c>
       <c r="O73">
-        <v>11.144169086</v>
+        <v>11.107185552</v>
       </c>
       <c r="P73">
-        <v>21.632798814</v>
+        <v>21.561007248</v>
       </c>
       <c r="Q73">
-        <v>26.932798814</v>
+        <v>26.861007248</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2275202560264731</v>
+        <v>0.2331667179759982</v>
       </c>
       <c r="T73">
-        <v>2.368424117104896</v>
+        <v>2.442016444949856</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.244054339745656</v>
+        <v>5.171220251693632</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0915652410332795</v>
+        <v>0.09123602781888178</v>
       </c>
       <c r="C74">
-        <v>86.55245338906064</v>
+        <v>85.25200943214335</v>
       </c>
       <c r="D74">
-        <v>156.1764533890606</v>
+        <v>156.8430094321433</v>
       </c>
       <c r="E74">
-        <v>92.324</v>
+        <v>94.29099999999998</v>
       </c>
       <c r="F74">
-        <v>141.624</v>
+        <v>143.591</v>
       </c>
       <c r="G74">
         <v>72</v>
@@ -7355,28 +7355,28 @@
         <v>40.5</v>
       </c>
       <c r="M74">
-        <v>7.8318072</v>
+        <v>7.940582299999999</v>
       </c>
       <c r="N74">
-        <v>32.6681928</v>
+        <v>32.5594177</v>
       </c>
       <c r="O74">
-        <v>11.107185552</v>
+        <v>11.070202018</v>
       </c>
       <c r="P74">
-        <v>21.561007248</v>
+        <v>21.489215682</v>
       </c>
       <c r="Q74">
-        <v>26.861007248</v>
+        <v>26.78921568199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2331667179759982</v>
+        <v>0.2392314363662288</v>
       </c>
       <c r="T74">
-        <v>2.442016444949856</v>
+        <v>2.521060056338887</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.171220251693632</v>
+        <v>5.100381618108788</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09123602781888178</v>
+        <v>0.09090681460448408</v>
       </c>
       <c r="C75">
-        <v>85.25200943214335</v>
+        <v>83.95727954186938</v>
       </c>
       <c r="D75">
-        <v>156.8430094321433</v>
+        <v>157.5152795418694</v>
       </c>
       <c r="E75">
-        <v>94.29099999999998</v>
+        <v>96.258</v>
       </c>
       <c r="F75">
-        <v>143.591</v>
+        <v>145.558</v>
       </c>
       <c r="G75">
         <v>72</v>
@@ -7437,28 +7437,28 @@
         <v>40.5</v>
       </c>
       <c r="M75">
-        <v>7.940582299999999</v>
+        <v>8.0493574</v>
       </c>
       <c r="N75">
-        <v>32.5594177</v>
+        <v>32.4506426</v>
       </c>
       <c r="O75">
-        <v>11.070202018</v>
+        <v>11.033218484</v>
       </c>
       <c r="P75">
-        <v>21.489215682</v>
+        <v>21.417424116</v>
       </c>
       <c r="Q75">
-        <v>26.78921568199999</v>
+        <v>26.717424116</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2392314363662288</v>
+        <v>0.245762671555708</v>
       </c>
       <c r="T75">
-        <v>2.521060056338887</v>
+        <v>2.606183945527075</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.100381618108788</v>
+        <v>5.031457542188399</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09090681460448408</v>
+        <v>0.09057760139008636</v>
       </c>
       <c r="C76">
-        <v>83.95727954186938</v>
+        <v>82.66833751047852</v>
       </c>
       <c r="D76">
-        <v>157.5152795418694</v>
+        <v>158.1933375104785</v>
       </c>
       <c r="E76">
-        <v>96.258</v>
+        <v>98.22499999999998</v>
       </c>
       <c r="F76">
-        <v>145.558</v>
+        <v>147.525</v>
       </c>
       <c r="G76">
         <v>72</v>
@@ -7519,28 +7519,28 @@
         <v>40.5</v>
       </c>
       <c r="M76">
-        <v>8.0493574</v>
+        <v>8.158132499999999</v>
       </c>
       <c r="N76">
-        <v>32.4506426</v>
+        <v>32.3418675</v>
       </c>
       <c r="O76">
-        <v>11.033218484</v>
+        <v>10.99623495</v>
       </c>
       <c r="P76">
-        <v>21.417424116</v>
+        <v>21.34563255</v>
       </c>
       <c r="Q76">
-        <v>26.717424116</v>
+        <v>26.64563254999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.245762671555708</v>
+        <v>0.2528164055603455</v>
       </c>
       <c r="T76">
-        <v>2.606183945527075</v>
+        <v>2.698117745850317</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.031457542188399</v>
+        <v>4.964371441625888</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09057760139008636</v>
+        <v>0.09024838817568866</v>
       </c>
       <c r="C77">
-        <v>82.66833751047852</v>
+        <v>81.38525840632113</v>
       </c>
       <c r="D77">
-        <v>158.1933375104785</v>
+        <v>158.8772584063211</v>
       </c>
       <c r="E77">
-        <v>98.22499999999998</v>
+        <v>100.192</v>
       </c>
       <c r="F77">
-        <v>147.525</v>
+        <v>149.492</v>
       </c>
       <c r="G77">
         <v>72</v>
@@ -7601,28 +7601,28 @@
         <v>40.5</v>
       </c>
       <c r="M77">
-        <v>8.158132499999999</v>
+        <v>8.2669076</v>
       </c>
       <c r="N77">
-        <v>32.3418675</v>
+        <v>32.2330924</v>
       </c>
       <c r="O77">
-        <v>10.99623495</v>
+        <v>10.959251416</v>
       </c>
       <c r="P77">
-        <v>21.34563255</v>
+        <v>21.273840984</v>
       </c>
       <c r="Q77">
-        <v>26.64563254999999</v>
+        <v>26.573840984</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2528164055603455</v>
+        <v>0.2604579507320361</v>
       </c>
       <c r="T77">
-        <v>2.698117745850317</v>
+        <v>2.797712696200497</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.964371441625888</v>
+        <v>4.899050764762389</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09024838817568866</v>
+        <v>0.08991917496129095</v>
       </c>
       <c r="C78">
-        <v>81.38525840632113</v>
+        <v>80.10811860156338</v>
       </c>
       <c r="D78">
-        <v>158.8772584063211</v>
+        <v>159.5671186015634</v>
       </c>
       <c r="E78">
-        <v>100.192</v>
+        <v>102.159</v>
       </c>
       <c r="F78">
-        <v>149.492</v>
+        <v>151.459</v>
       </c>
       <c r="G78">
         <v>72</v>
@@ -7683,28 +7683,28 @@
         <v>40.5</v>
       </c>
       <c r="M78">
-        <v>8.2669076</v>
+        <v>8.3756827</v>
       </c>
       <c r="N78">
-        <v>32.2330924</v>
+        <v>32.1243173</v>
       </c>
       <c r="O78">
-        <v>10.959251416</v>
+        <v>10.922267882</v>
       </c>
       <c r="P78">
-        <v>21.273840984</v>
+        <v>21.202049418</v>
       </c>
       <c r="Q78">
-        <v>26.573840984</v>
+        <v>26.502049418</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2604579507320361</v>
+        <v>0.2687639780925694</v>
       </c>
       <c r="T78">
-        <v>2.797712696200497</v>
+        <v>2.90596807701591</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.899050764762389</v>
+        <v>4.835426728856383</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08991917496129095</v>
+        <v>0.08958996174689324</v>
       </c>
       <c r="C79">
-        <v>80.10811860156338</v>
+        <v>78.83699580061716</v>
       </c>
       <c r="D79">
-        <v>159.5671186015634</v>
+        <v>160.2629958006171</v>
       </c>
       <c r="E79">
-        <v>102.159</v>
+        <v>104.126</v>
       </c>
       <c r="F79">
-        <v>151.459</v>
+        <v>153.426</v>
       </c>
       <c r="G79">
         <v>72</v>
@@ -7765,28 +7765,28 @@
         <v>40.5</v>
       </c>
       <c r="M79">
-        <v>8.3756827</v>
+        <v>8.484457799999999</v>
       </c>
       <c r="N79">
-        <v>32.1243173</v>
+        <v>32.0155422</v>
       </c>
       <c r="O79">
-        <v>10.922267882</v>
+        <v>10.885284348</v>
       </c>
       <c r="P79">
-        <v>21.202049418</v>
+        <v>21.130257852</v>
       </c>
       <c r="Q79">
-        <v>26.502049418</v>
+        <v>26.430257852</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2687639780925694</v>
+        <v>0.2778250988495147</v>
       </c>
       <c r="T79">
-        <v>2.90596807701591</v>
+        <v>3.024064856087269</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.835426728856383</v>
+        <v>4.77343407848643</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08958996174689324</v>
+        <v>0.08926074853249552</v>
       </c>
       <c r="C80">
-        <v>78.83699580061716</v>
+        <v>77.57196906931685</v>
       </c>
       <c r="D80">
-        <v>160.2629958006171</v>
+        <v>160.9649690693169</v>
       </c>
       <c r="E80">
-        <v>104.126</v>
+        <v>106.093</v>
       </c>
       <c r="F80">
-        <v>153.426</v>
+        <v>155.393</v>
       </c>
       <c r="G80">
         <v>72</v>
@@ -7847,28 +7847,28 @@
         <v>40.5</v>
       </c>
       <c r="M80">
-        <v>8.484457799999999</v>
+        <v>8.5932329</v>
       </c>
       <c r="N80">
-        <v>32.0155422</v>
+        <v>31.9067671</v>
       </c>
       <c r="O80">
-        <v>10.885284348</v>
+        <v>10.848300814</v>
       </c>
       <c r="P80">
-        <v>21.130257852</v>
+        <v>21.058466286</v>
       </c>
       <c r="Q80">
-        <v>26.430257852</v>
+        <v>26.358466286</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2778250988495147</v>
+        <v>0.287749183488074</v>
       </c>
       <c r="T80">
-        <v>3.024064856087269</v>
+        <v>3.153408947451139</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.77343407848643</v>
+        <v>4.713010862303057</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08926074853249552</v>
+        <v>0.08893153531809782</v>
       </c>
       <c r="C81">
-        <v>77.57196906931685</v>
+        <v>76.31311886486679</v>
       </c>
       <c r="D81">
-        <v>160.9649690693169</v>
+        <v>161.6731188648668</v>
       </c>
       <c r="E81">
-        <v>106.093</v>
+        <v>108.06</v>
       </c>
       <c r="F81">
-        <v>155.393</v>
+        <v>157.36</v>
       </c>
       <c r="G81">
         <v>72</v>
@@ -7929,28 +7929,28 @@
         <v>40.5</v>
       </c>
       <c r="M81">
-        <v>8.5932329</v>
+        <v>8.702008000000001</v>
       </c>
       <c r="N81">
-        <v>31.9067671</v>
+        <v>31.797992</v>
       </c>
       <c r="O81">
-        <v>10.848300814</v>
+        <v>10.81131728</v>
       </c>
       <c r="P81">
-        <v>21.058466286</v>
+        <v>20.98667472</v>
       </c>
       <c r="Q81">
-        <v>26.358466286</v>
+        <v>26.28667472</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.287749183488074</v>
+        <v>0.2986656765904891</v>
       </c>
       <c r="T81">
-        <v>3.153408947451139</v>
+        <v>3.295687447951395</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.713010862303057</v>
+        <v>4.654098226524269</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08893153531809782</v>
+        <v>0.0886023221037001</v>
       </c>
       <c r="C82">
-        <v>76.31311886486679</v>
+        <v>75.06052706658281</v>
       </c>
       <c r="D82">
-        <v>161.6731188648668</v>
+        <v>162.3875270665828</v>
       </c>
       <c r="E82">
-        <v>108.06</v>
+        <v>110.027</v>
       </c>
       <c r="F82">
-        <v>157.36</v>
+        <v>159.327</v>
       </c>
       <c r="G82">
         <v>72</v>
@@ -8011,28 +8011,28 @@
         <v>40.5</v>
       </c>
       <c r="M82">
-        <v>8.702008000000001</v>
+        <v>8.8107831</v>
       </c>
       <c r="N82">
-        <v>31.797992</v>
+        <v>31.6892169</v>
       </c>
       <c r="O82">
-        <v>10.81131728</v>
+        <v>10.774333746</v>
       </c>
       <c r="P82">
-        <v>20.98667472</v>
+        <v>20.914883154</v>
       </c>
       <c r="Q82">
-        <v>26.28667472</v>
+        <v>26.214883154</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2986656765904891</v>
+        <v>0.3107312742300006</v>
       </c>
       <c r="T82">
-        <v>3.295687447951395</v>
+        <v>3.452942632714837</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.654098226524269</v>
+        <v>4.596640223727673</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0886023221037001</v>
+        <v>0.0882731088893024</v>
       </c>
       <c r="C83">
-        <v>75.06052706658281</v>
+        <v>73.81427700745127</v>
       </c>
       <c r="D83">
-        <v>162.3875270665828</v>
+        <v>163.1082770074513</v>
       </c>
       <c r="E83">
-        <v>110.027</v>
+        <v>111.994</v>
       </c>
       <c r="F83">
-        <v>159.327</v>
+        <v>161.294</v>
       </c>
       <c r="G83">
         <v>72</v>
@@ -8093,28 +8093,28 @@
         <v>40.5</v>
       </c>
       <c r="M83">
-        <v>8.8107831</v>
+        <v>8.919558200000001</v>
       </c>
       <c r="N83">
-        <v>31.6892169</v>
+        <v>31.5804418</v>
       </c>
       <c r="O83">
-        <v>10.774333746</v>
+        <v>10.737350212</v>
       </c>
       <c r="P83">
-        <v>20.914883154</v>
+        <v>20.843091588</v>
       </c>
       <c r="Q83">
-        <v>26.214883154</v>
+        <v>26.143091588</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3107312742300006</v>
+        <v>0.3241374938294579</v>
       </c>
       <c r="T83">
-        <v>3.452942632714837</v>
+        <v>3.627670615785327</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.596640223727673</v>
+        <v>4.540583635633433</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0882731088893024</v>
+        <v>0.08931339567490469</v>
       </c>
       <c r="C84">
-        <v>73.81427700745127</v>
+        <v>69.59129807371747</v>
       </c>
       <c r="D84">
-        <v>163.1082770074513</v>
+        <v>160.8522980737175</v>
       </c>
       <c r="E84">
-        <v>111.994</v>
+        <v>113.961</v>
       </c>
       <c r="F84">
-        <v>161.294</v>
+        <v>163.261</v>
       </c>
       <c r="G84">
         <v>72</v>
@@ -8175,45 +8175,45 @@
         <v>40.5</v>
       </c>
       <c r="M84">
-        <v>8.919558200000001</v>
+        <v>9.4364858</v>
       </c>
       <c r="N84">
-        <v>31.5804418</v>
+        <v>31.0635142</v>
       </c>
       <c r="O84">
-        <v>10.737350212</v>
+        <v>10.561594828</v>
       </c>
       <c r="P84">
-        <v>20.843091588</v>
+        <v>20.501919372</v>
       </c>
       <c r="Q84">
-        <v>26.143091588</v>
+        <v>25.801919372</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3241374938294579</v>
+        <v>0.3391209157347336</v>
       </c>
       <c r="T84">
-        <v>3.627670615785327</v>
+        <v>3.822954832158229</v>
       </c>
       <c r="U84">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V84">
         <v>0.34</v>
       </c>
       <c r="W84">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.540583635633433</v>
+        <v>4.291851951920492</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08931339567490469</v>
+        <v>0.08900068246050698</v>
       </c>
       <c r="C85">
-        <v>69.59129807371747</v>
+        <v>68.29586436352551</v>
       </c>
       <c r="D85">
-        <v>160.8522980737175</v>
+        <v>161.5238643635255</v>
       </c>
       <c r="E85">
-        <v>113.961</v>
+        <v>115.928</v>
       </c>
       <c r="F85">
-        <v>163.261</v>
+        <v>165.228</v>
       </c>
       <c r="G85">
         <v>72</v>
@@ -8257,28 +8257,28 @@
         <v>40.5</v>
       </c>
       <c r="M85">
-        <v>9.4364858</v>
+        <v>9.550178400000002</v>
       </c>
       <c r="N85">
-        <v>31.0635142</v>
+        <v>30.9498216</v>
       </c>
       <c r="O85">
-        <v>10.561594828</v>
+        <v>10.522939344</v>
       </c>
       <c r="P85">
-        <v>20.501919372</v>
+        <v>20.426882256</v>
       </c>
       <c r="Q85">
-        <v>25.801919372</v>
+        <v>25.726882256</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3391209157347336</v>
+        <v>0.3559772653781688</v>
       </c>
       <c r="T85">
-        <v>3.822954832158229</v>
+        <v>4.042649575577743</v>
       </c>
       <c r="U85">
         <v>0.0578</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>4.291851951920492</v>
+        <v>4.240758476302389</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08900068246050699</v>
+        <v>0.08868796924610928</v>
       </c>
       <c r="C86">
-        <v>68.29586436352551</v>
+        <v>67.00606180854905</v>
       </c>
       <c r="D86">
-        <v>161.5238643635255</v>
+        <v>162.201061808549</v>
       </c>
       <c r="E86">
-        <v>115.928</v>
+        <v>117.895</v>
       </c>
       <c r="F86">
-        <v>165.228</v>
+        <v>167.195</v>
       </c>
       <c r="G86">
         <v>72</v>
@@ -8339,28 +8339,28 @@
         <v>40.5</v>
       </c>
       <c r="M86">
-        <v>9.5501784</v>
+        <v>9.663871</v>
       </c>
       <c r="N86">
-        <v>30.9498216</v>
+        <v>30.836129</v>
       </c>
       <c r="O86">
-        <v>10.522939344</v>
+        <v>10.48428386</v>
       </c>
       <c r="P86">
-        <v>20.426882256</v>
+        <v>20.35184514</v>
       </c>
       <c r="Q86">
-        <v>25.726882256</v>
+        <v>25.65184514</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3559772653781686</v>
+        <v>0.3750811283073952</v>
       </c>
       <c r="T86">
-        <v>4.04264957557774</v>
+        <v>4.29163695145319</v>
       </c>
       <c r="U86">
         <v>0.0578</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.240758476302391</v>
+        <v>4.190867200110597</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08868796924610928</v>
+        <v>0.08837525603171156</v>
       </c>
       <c r="C87">
-        <v>67.00606180854905</v>
+        <v>65.7219615337421</v>
       </c>
       <c r="D87">
-        <v>162.201061808549</v>
+        <v>162.8839615337421</v>
       </c>
       <c r="E87">
-        <v>117.895</v>
+        <v>119.862</v>
       </c>
       <c r="F87">
-        <v>167.195</v>
+        <v>169.162</v>
       </c>
       <c r="G87">
         <v>72</v>
@@ -8421,28 +8421,28 @@
         <v>40.5</v>
       </c>
       <c r="M87">
-        <v>9.663871</v>
+        <v>9.777563599999999</v>
       </c>
       <c r="N87">
-        <v>30.836129</v>
+        <v>30.7224364</v>
       </c>
       <c r="O87">
-        <v>10.48428386</v>
+        <v>10.445628376</v>
       </c>
       <c r="P87">
-        <v>20.35184514</v>
+        <v>20.276808024</v>
       </c>
       <c r="Q87">
-        <v>25.65184514</v>
+        <v>25.57680802399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3750811283073952</v>
+        <v>0.3969141145122255</v>
       </c>
       <c r="T87">
-        <v>4.29163695145319</v>
+        <v>4.576193952453703</v>
       </c>
       <c r="U87">
         <v>0.0578</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.190867200110597</v>
+        <v>4.142136186155824</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08837525603171156</v>
+        <v>0.08806254281731385</v>
       </c>
       <c r="C88">
-        <v>65.7219615337421</v>
+        <v>64.44363586692538</v>
       </c>
       <c r="D88">
-        <v>162.8839615337421</v>
+        <v>163.5726358669254</v>
       </c>
       <c r="E88">
-        <v>119.862</v>
+        <v>121.829</v>
       </c>
       <c r="F88">
-        <v>169.162</v>
+        <v>171.129</v>
       </c>
       <c r="G88">
         <v>72</v>
@@ -8503,28 +8503,28 @@
         <v>40.5</v>
       </c>
       <c r="M88">
-        <v>9.777563599999999</v>
+        <v>9.891256200000001</v>
       </c>
       <c r="N88">
-        <v>30.7224364</v>
+        <v>30.6087438</v>
       </c>
       <c r="O88">
-        <v>10.445628376</v>
+        <v>10.406972892</v>
       </c>
       <c r="P88">
-        <v>20.276808024</v>
+        <v>20.201770908</v>
       </c>
       <c r="Q88">
-        <v>25.57680802399999</v>
+        <v>25.501770908</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3969141145122255</v>
+        <v>0.422106021671645</v>
       </c>
       <c r="T88">
-        <v>4.576193952453703</v>
+        <v>4.90452895360814</v>
       </c>
       <c r="U88">
         <v>0.0578</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.142136186155824</v>
+        <v>4.09452542539541</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08806254281731385</v>
+        <v>0.08774982960291614</v>
       </c>
       <c r="C89">
-        <v>64.44363586692538</v>
+        <v>63.17115836432316</v>
       </c>
       <c r="D89">
-        <v>163.5726358669254</v>
+        <v>164.2671583643232</v>
       </c>
       <c r="E89">
-        <v>121.829</v>
+        <v>123.796</v>
       </c>
       <c r="F89">
-        <v>171.129</v>
+        <v>173.096</v>
       </c>
       <c r="G89">
         <v>72</v>
@@ -8585,28 +8585,28 @@
         <v>40.5</v>
       </c>
       <c r="M89">
-        <v>9.891256200000001</v>
+        <v>10.0049488</v>
       </c>
       <c r="N89">
-        <v>30.6087438</v>
+        <v>30.4950512</v>
       </c>
       <c r="O89">
-        <v>10.406972892</v>
+        <v>10.368317408</v>
       </c>
       <c r="P89">
-        <v>20.201770908</v>
+        <v>20.126733792</v>
       </c>
       <c r="Q89">
-        <v>25.501770908</v>
+        <v>25.42673379199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.422106021671645</v>
+        <v>0.4514965800243012</v>
       </c>
       <c r="T89">
-        <v>4.90452895360814</v>
+        <v>5.287586454954985</v>
       </c>
       <c r="U89">
         <v>0.0578</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.09452542539541</v>
+        <v>4.047996727379553</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08774982960291614</v>
+        <v>0.08743711638851843</v>
       </c>
       <c r="C90">
-        <v>63.17115836432316</v>
+        <v>61.90460383675318</v>
       </c>
       <c r="D90">
-        <v>164.2671583643232</v>
+        <v>164.9676038367532</v>
       </c>
       <c r="E90">
-        <v>123.796</v>
+        <v>125.763</v>
       </c>
       <c r="F90">
-        <v>173.096</v>
+        <v>175.063</v>
       </c>
       <c r="G90">
         <v>72</v>
@@ -8667,28 +8667,28 @@
         <v>40.5</v>
       </c>
       <c r="M90">
-        <v>10.0049488</v>
+        <v>10.1186414</v>
       </c>
       <c r="N90">
-        <v>30.4950512</v>
+        <v>30.3813586</v>
       </c>
       <c r="O90">
-        <v>10.368317408</v>
+        <v>10.329661924</v>
       </c>
       <c r="P90">
-        <v>20.126733792</v>
+        <v>20.051696676</v>
       </c>
       <c r="Q90">
-        <v>25.42673379199999</v>
+        <v>25.351696676</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4514965800243012</v>
+        <v>0.4862308762592585</v>
       </c>
       <c r="T90">
-        <v>5.287586454954985</v>
+        <v>5.740290774728528</v>
       </c>
       <c r="U90">
         <v>0.0578</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.047996727379553</v>
+        <v>4.002513618083155</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08743711638851843</v>
+        <v>0.0892034031741207</v>
       </c>
       <c r="C91">
-        <v>61.90460383675318</v>
+        <v>56.05787453054106</v>
       </c>
       <c r="D91">
-        <v>164.9676038367532</v>
+        <v>161.0878745305411</v>
       </c>
       <c r="E91">
-        <v>125.763</v>
+        <v>127.73</v>
       </c>
       <c r="F91">
-        <v>175.063</v>
+        <v>177.03</v>
       </c>
       <c r="G91">
         <v>72</v>
@@ -8749,45 +8749,45 @@
         <v>40.5</v>
       </c>
       <c r="M91">
-        <v>10.1186414</v>
+        <v>10.851939</v>
       </c>
       <c r="N91">
-        <v>30.3813586</v>
+        <v>29.648061</v>
       </c>
       <c r="O91">
-        <v>10.329661924</v>
+        <v>10.08034074</v>
       </c>
       <c r="P91">
-        <v>20.051696676</v>
+        <v>19.56772026</v>
       </c>
       <c r="Q91">
-        <v>25.351696676</v>
+        <v>24.86772026</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4862308762592585</v>
+        <v>0.5279120317412073</v>
       </c>
       <c r="T91">
-        <v>5.740290774728528</v>
+        <v>6.28353595845678</v>
       </c>
       <c r="U91">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V91">
         <v>0.34</v>
       </c>
       <c r="W91">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>4.002513618083155</v>
+        <v>3.732051940210869</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0892034031741207</v>
+        <v>0.08891378995972299</v>
       </c>
       <c r="C92">
-        <v>56.05787453054106</v>
+        <v>54.71446680982947</v>
       </c>
       <c r="D92">
-        <v>161.0878745305411</v>
+        <v>161.7114668098295</v>
       </c>
       <c r="E92">
-        <v>127.73</v>
+        <v>129.697</v>
       </c>
       <c r="F92">
-        <v>177.03</v>
+        <v>178.997</v>
       </c>
       <c r="G92">
         <v>72</v>
@@ -8831,28 +8831,28 @@
         <v>40.5</v>
       </c>
       <c r="M92">
-        <v>10.851939</v>
+        <v>10.9725161</v>
       </c>
       <c r="N92">
-        <v>29.648061</v>
+        <v>29.5274839</v>
       </c>
       <c r="O92">
-        <v>10.08034074</v>
+        <v>10.039344526</v>
       </c>
       <c r="P92">
-        <v>19.56772026</v>
+        <v>19.488139374</v>
       </c>
       <c r="Q92">
-        <v>24.86772026</v>
+        <v>24.788139374</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5279120317412073</v>
+        <v>0.5788556662191446</v>
       </c>
       <c r="T92">
-        <v>6.28353595845678</v>
+        <v>6.947502294124645</v>
       </c>
       <c r="U92">
         <v>0.0613</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.732051940210869</v>
+        <v>3.691040380428332</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08891378995972299</v>
+        <v>0.0886241767453253</v>
       </c>
       <c r="C93">
-        <v>54.71446680982947</v>
+        <v>53.37590586654809</v>
       </c>
       <c r="D93">
-        <v>161.7114668098295</v>
+        <v>162.3399058665481</v>
       </c>
       <c r="E93">
-        <v>129.697</v>
+        <v>131.664</v>
       </c>
       <c r="F93">
-        <v>178.997</v>
+        <v>180.964</v>
       </c>
       <c r="G93">
         <v>72</v>
@@ -8913,28 +8913,28 @@
         <v>40.5</v>
       </c>
       <c r="M93">
-        <v>10.9725161</v>
+        <v>11.0930932</v>
       </c>
       <c r="N93">
-        <v>29.5274839</v>
+        <v>29.4069068</v>
       </c>
       <c r="O93">
-        <v>10.039344526</v>
+        <v>9.998348312000001</v>
       </c>
       <c r="P93">
-        <v>19.488139374</v>
+        <v>19.408558488</v>
       </c>
       <c r="Q93">
-        <v>24.788139374</v>
+        <v>24.708558488</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5788556662191446</v>
+        <v>0.6425352093165666</v>
       </c>
       <c r="T93">
-        <v>6.947502294124645</v>
+        <v>7.777460213709476</v>
       </c>
       <c r="U93">
         <v>0.0613</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.691040380428332</v>
+        <v>3.650920376293242</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0886241767453253</v>
+        <v>0.08833456353092758</v>
       </c>
       <c r="C94">
-        <v>53.37590586654809</v>
+        <v>52.04224842742258</v>
       </c>
       <c r="D94">
-        <v>162.3399058665481</v>
+        <v>162.9732484274226</v>
       </c>
       <c r="E94">
-        <v>131.664</v>
+        <v>133.631</v>
       </c>
       <c r="F94">
-        <v>180.964</v>
+        <v>182.931</v>
       </c>
       <c r="G94">
         <v>72</v>
@@ -8995,28 +8995,28 @@
         <v>40.5</v>
       </c>
       <c r="M94">
-        <v>11.0930932</v>
+        <v>11.2136703</v>
       </c>
       <c r="N94">
-        <v>29.4069068</v>
+        <v>29.2863297</v>
       </c>
       <c r="O94">
-        <v>9.998348312000001</v>
+        <v>9.957352098000001</v>
       </c>
       <c r="P94">
-        <v>19.408558488</v>
+        <v>19.328977602</v>
       </c>
       <c r="Q94">
-        <v>24.708558488</v>
+        <v>24.628977602</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6425352093165666</v>
+        <v>0.7244089075846804</v>
       </c>
       <c r="T94">
-        <v>7.777460213709476</v>
+        <v>8.844548967461401</v>
       </c>
       <c r="U94">
         <v>0.0613</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.650920376293242</v>
+        <v>3.611663167946003</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08833456353092758</v>
+        <v>0.08804495031652988</v>
       </c>
       <c r="C95">
-        <v>52.04224842742258</v>
+        <v>50.7135521078857</v>
       </c>
       <c r="D95">
-        <v>162.9732484274226</v>
+        <v>163.6115521078857</v>
       </c>
       <c r="E95">
-        <v>133.631</v>
+        <v>135.598</v>
       </c>
       <c r="F95">
-        <v>182.931</v>
+        <v>184.898</v>
       </c>
       <c r="G95">
         <v>72</v>
@@ -9077,28 +9077,28 @@
         <v>40.5</v>
       </c>
       <c r="M95">
-        <v>11.2136703</v>
+        <v>11.3342474</v>
       </c>
       <c r="N95">
-        <v>29.2863297</v>
+        <v>29.1657526</v>
       </c>
       <c r="O95">
-        <v>9.957352098000001</v>
+        <v>9.916355884</v>
       </c>
       <c r="P95">
-        <v>19.328977602</v>
+        <v>19.249396716</v>
       </c>
       <c r="Q95">
-        <v>24.628977602</v>
+        <v>24.549396716</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7244089075846804</v>
+        <v>0.8335738386088322</v>
       </c>
       <c r="T95">
-        <v>8.844548967461401</v>
+        <v>10.26733397246397</v>
       </c>
       <c r="U95">
         <v>0.0613</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.611663167946003</v>
+        <v>3.573241219350832</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08804495031652988</v>
+        <v>0.08775533710213218</v>
       </c>
       <c r="C96">
-        <v>50.7135521078857</v>
+        <v>49.38987542954965</v>
       </c>
       <c r="D96">
-        <v>163.6115521078857</v>
+        <v>164.2548754295497</v>
       </c>
       <c r="E96">
-        <v>135.598</v>
+        <v>137.565</v>
       </c>
       <c r="F96">
-        <v>184.898</v>
+        <v>186.865</v>
       </c>
       <c r="G96">
         <v>72</v>
@@ -9159,28 +9159,28 @@
         <v>40.5</v>
       </c>
       <c r="M96">
-        <v>11.3342474</v>
+        <v>11.4548245</v>
       </c>
       <c r="N96">
-        <v>29.1657526</v>
+        <v>29.0451755</v>
       </c>
       <c r="O96">
-        <v>9.916355884</v>
+        <v>9.87535967</v>
       </c>
       <c r="P96">
-        <v>19.249396716</v>
+        <v>19.16981583</v>
       </c>
       <c r="Q96">
-        <v>24.549396716</v>
+        <v>24.46981582999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8335738386088322</v>
+        <v>0.9864047420426448</v>
       </c>
       <c r="T96">
-        <v>10.26733397246397</v>
+        <v>12.25923297946757</v>
       </c>
       <c r="U96">
         <v>0.0613</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.573241219350832</v>
+        <v>3.535628153883981</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08775533710213218</v>
+        <v>0.08923980388773446</v>
       </c>
       <c r="C97">
-        <v>49.38987542954965</v>
+        <v>44.17783694081848</v>
       </c>
       <c r="D97">
-        <v>164.2548754295497</v>
+        <v>161.0098369408185</v>
       </c>
       <c r="E97">
-        <v>137.565</v>
+        <v>139.532</v>
       </c>
       <c r="F97">
-        <v>186.865</v>
+        <v>188.832</v>
       </c>
       <c r="G97">
         <v>72</v>
@@ -9241,45 +9241,45 @@
         <v>40.5</v>
       </c>
       <c r="M97">
-        <v>11.4548245</v>
+        <v>12.1041312</v>
       </c>
       <c r="N97">
-        <v>29.0451755</v>
+        <v>28.3958688</v>
       </c>
       <c r="O97">
-        <v>9.87535967</v>
+        <v>9.654595392000001</v>
       </c>
       <c r="P97">
-        <v>19.16981583</v>
+        <v>18.741273408</v>
       </c>
       <c r="Q97">
-        <v>24.46981582999999</v>
+        <v>24.041273408</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9864047420426448</v>
+        <v>1.215651097193364</v>
       </c>
       <c r="T97">
-        <v>12.25923297946757</v>
+        <v>15.24708148997296</v>
       </c>
       <c r="U97">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V97">
         <v>0.34</v>
       </c>
       <c r="W97">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>3.535628153883981</v>
+        <v>3.345965053650442</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08923980388773445</v>
+        <v>0.08896867067333675</v>
       </c>
       <c r="C98">
-        <v>44.17783694081851</v>
+        <v>42.7939277157742</v>
       </c>
       <c r="D98">
-        <v>161.0098369408185</v>
+        <v>161.5929277157742</v>
       </c>
       <c r="E98">
-        <v>139.532</v>
+        <v>141.499</v>
       </c>
       <c r="F98">
-        <v>188.832</v>
+        <v>190.799</v>
       </c>
       <c r="G98">
         <v>72</v>
@@ -9323,28 +9323,28 @@
         <v>40.5</v>
       </c>
       <c r="M98">
-        <v>12.1041312</v>
+        <v>12.2302159</v>
       </c>
       <c r="N98">
-        <v>28.3958688</v>
+        <v>28.2697841</v>
       </c>
       <c r="O98">
-        <v>9.654595392000001</v>
+        <v>9.611726594000002</v>
       </c>
       <c r="P98">
-        <v>18.741273408</v>
+        <v>18.658057506</v>
       </c>
       <c r="Q98">
-        <v>24.041273408</v>
+        <v>23.958057506</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.215651097193361</v>
+        <v>1.597728355777891</v>
       </c>
       <c r="T98">
-        <v>15.24708148997292</v>
+        <v>20.22682900748189</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.345965053650442</v>
+        <v>3.311470568561263</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08896867067333675</v>
+        <v>0.08869753745893905</v>
       </c>
       <c r="C99">
-        <v>42.7939277157742</v>
+        <v>41.41425712125709</v>
       </c>
       <c r="D99">
-        <v>161.5929277157742</v>
+        <v>162.1802571212571</v>
       </c>
       <c r="E99">
-        <v>141.499</v>
+        <v>143.466</v>
       </c>
       <c r="F99">
-        <v>190.799</v>
+        <v>192.766</v>
       </c>
       <c r="G99">
         <v>72</v>
@@ -9405,28 +9405,28 @@
         <v>40.5</v>
       </c>
       <c r="M99">
-        <v>12.2302159</v>
+        <v>12.3563006</v>
       </c>
       <c r="N99">
-        <v>28.2697841</v>
+        <v>28.1436994</v>
       </c>
       <c r="O99">
-        <v>9.611726594000002</v>
+        <v>9.568857796</v>
       </c>
       <c r="P99">
-        <v>18.658057506</v>
+        <v>18.574841604</v>
       </c>
       <c r="Q99">
-        <v>23.958057506</v>
+        <v>23.874841604</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.597728355777891</v>
+        <v>2.36188287294695</v>
       </c>
       <c r="T99">
-        <v>20.22682900748189</v>
+        <v>30.18632404249983</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.311470568561263</v>
+        <v>3.277680052555536</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08869753745893905</v>
+        <v>0.08842640424454133</v>
       </c>
       <c r="C100">
-        <v>41.41425712125709</v>
+        <v>40.03887154333779</v>
       </c>
       <c r="D100">
-        <v>162.1802571212571</v>
+        <v>162.7718715433378</v>
       </c>
       <c r="E100">
-        <v>143.466</v>
+        <v>145.433</v>
       </c>
       <c r="F100">
-        <v>192.766</v>
+        <v>194.733</v>
       </c>
       <c r="G100">
         <v>72</v>
@@ -9487,28 +9487,28 @@
         <v>40.5</v>
       </c>
       <c r="M100">
-        <v>12.3563006</v>
+        <v>12.4823853</v>
       </c>
       <c r="N100">
-        <v>28.1436994</v>
+        <v>28.0176147</v>
       </c>
       <c r="O100">
-        <v>9.568857796</v>
+        <v>9.525988998000003</v>
       </c>
       <c r="P100">
-        <v>18.574841604</v>
+        <v>18.491625702</v>
       </c>
       <c r="Q100">
-        <v>23.874841604</v>
+        <v>23.791625702</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.36188287294695</v>
+        <v>4.65434642445413</v>
       </c>
       <c r="T100">
-        <v>30.18632404249983</v>
+        <v>60.06480914755366</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.277680052555536</v>
+        <v>3.244572173236794</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08842640424454133</v>
-      </c>
-      <c r="C101">
-        <v>40.03887154333779</v>
-      </c>
-      <c r="D101">
-        <v>162.7718715433378</v>
-      </c>
-      <c r="E101">
-        <v>145.433</v>
-      </c>
-      <c r="F101">
-        <v>194.733</v>
-      </c>
-      <c r="G101">
-        <v>72</v>
-      </c>
-      <c r="H101">
-        <v>147.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>45.8</v>
-      </c>
-      <c r="K101">
-        <v>5.299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>40.5</v>
-      </c>
-      <c r="M101">
-        <v>12.4823853</v>
-      </c>
-      <c r="N101">
-        <v>28.0176147</v>
-      </c>
-      <c r="O101">
-        <v>9.525988998000003</v>
-      </c>
-      <c r="P101">
-        <v>18.491625702</v>
-      </c>
-      <c r="Q101">
-        <v>23.791625702</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.65434642445413</v>
-      </c>
-      <c r="T101">
-        <v>60.06480914755366</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.34</v>
-      </c>
-      <c r="W101">
-        <v>0.042306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.244572173236794</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
